--- a/Asos.xlsx
+++ b/Asos.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/b4a63f789af4ef06/Documents/Career/Career Development/Financial Statements/3 Statement Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4563" documentId="8_{8B7479BD-CF16-405B-9E54-99D78F102801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE0C4748-1561-4045-A4A1-8DE542193BDF}"/>
+  <xr:revisionPtr revIDLastSave="4600" documentId="8_{8B7479BD-CF16-405B-9E54-99D78F102801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9AF45FFD-2890-49DB-ACD2-4C33F136E0E9}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="1" xr2:uid="{C4FDF26E-8D02-42E6-9BA6-E8E4AB263931}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="6" xr2:uid="{C4FDF26E-8D02-42E6-9BA6-E8E4AB263931}"/>
   </bookViews>
   <sheets>
     <sheet name="Cover" sheetId="1" r:id="rId1"/>
@@ -70,7 +70,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="631" uniqueCount="440">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="632" uniqueCount="441">
   <si>
     <t>Financial Statements - Income Statement</t>
   </si>
@@ -1390,6 +1390,9 @@
   </si>
   <si>
     <t>Total Warehouse Costs</t>
+  </si>
+  <si>
+    <t>Minimum cash requirement</t>
   </si>
 </sst>
 </file>
@@ -2737,8 +2740,8 @@
     <xf numFmtId="196" fontId="29" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="204" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="204" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="202" fontId="29" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="202" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="202" fontId="29" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="202" fontId="25" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10095,31 +10098,31 @@
       <c r="D25" s="185"/>
       <c r="E25" s="185"/>
       <c r="F25" s="264">
-        <f t="shared" ref="F25" si="16">F18-F24</f>
-        <v>-503200000</v>
+        <f t="shared" ref="F25" si="16">F18+F24</f>
+        <v>-160600000</v>
       </c>
       <c r="G25" s="264">
-        <f t="shared" ref="G25" si="17">G18-G24</f>
-        <v>-378500000</v>
+        <f>G18+G24</f>
+        <v>-46100000</v>
       </c>
       <c r="H25" s="208">
-        <f>H18+H24</f>
+        <f t="shared" ref="H25:L25" si="17">H18+H24</f>
         <v>32565287.80053395</v>
       </c>
       <c r="I25" s="208">
-        <f t="shared" ref="I25:L25" si="18">I18+I24</f>
+        <f t="shared" si="17"/>
         <v>36311063.075144559</v>
       </c>
       <c r="J25" s="208">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>52614712.322024286</v>
       </c>
       <c r="K25" s="208">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>79561954.52051115</v>
       </c>
       <c r="L25" s="208">
-        <f t="shared" si="18"/>
+        <f t="shared" si="17"/>
         <v>114599035.87573484</v>
       </c>
     </row>
@@ -10132,31 +10135,31 @@
       <c r="D26" s="277"/>
       <c r="E26" s="277"/>
       <c r="F26" s="286">
-        <f t="shared" ref="F26:L26" si="19">F25/F10</f>
-        <v>-0.17317089958015006</v>
+        <f t="shared" ref="F26:L26" si="18">F25/F10</f>
+        <v>-5.5268772799229128E-2</v>
       </c>
       <c r="G26" s="286">
-        <f t="shared" si="19"/>
-        <v>-0.15275647752038099</v>
+        <f t="shared" si="18"/>
+        <v>-1.8605214303010736E-2</v>
       </c>
       <c r="H26" s="286">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1.3188987759916469E-2</v>
       </c>
       <c r="I26" s="286">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>1.4669105489611249E-2</v>
       </c>
       <c r="J26" s="286">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.0594437205472667E-2</v>
       </c>
       <c r="K26" s="286">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>2.9731618435900255E-2</v>
       </c>
       <c r="L26" s="286">
-        <f t="shared" si="19"/>
+        <f t="shared" si="18"/>
         <v>4.0308840749099045E-2</v>
       </c>
     </row>
@@ -10257,27 +10260,27 @@
         <v>-47400000</v>
       </c>
       <c r="G30" s="181">
-        <f t="shared" ref="G30:L30" si="20">SUM(G28:G29)</f>
+        <f t="shared" ref="G30:L30" si="19">SUM(G28:G29)</f>
         <v>-69300000</v>
       </c>
       <c r="H30" s="181">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>-51850600</v>
       </c>
       <c r="I30" s="181">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>-52275550.944315225</v>
       </c>
       <c r="J30" s="181">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>-58782485.266132593</v>
       </c>
       <c r="K30" s="181">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>-73942495.403930083</v>
       </c>
       <c r="L30" s="181">
-        <f t="shared" si="20"/>
+        <f t="shared" si="19"/>
         <v>-89019113.399617612</v>
       </c>
     </row>
@@ -10290,31 +10293,31 @@
       <c r="D31" s="185"/>
       <c r="E31" s="185"/>
       <c r="F31" s="264">
-        <f t="shared" ref="F31:L31" si="21">F18+F30</f>
+        <f t="shared" ref="F31:L31" si="20">F18+F30</f>
         <v>-379300000</v>
       </c>
       <c r="G31" s="264">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>-281600000</v>
       </c>
       <c r="H31" s="208">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>-165041562.09016538</v>
       </c>
       <c r="I31" s="208">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>-182239030.44808081</v>
       </c>
       <c r="J31" s="208">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>-193316137.6387279</v>
       </c>
       <c r="K31" s="208">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>-203235424.54314363</v>
       </c>
       <c r="L31" s="208">
-        <f t="shared" si="21"/>
+        <f t="shared" si="20"/>
         <v>-206177531.09173626</v>
       </c>
     </row>
@@ -10351,7 +10354,7 @@
         <v>0</v>
       </c>
       <c r="I33" s="236">
-        <f t="shared" ref="I33" si="22">-I649</f>
+        <f t="shared" ref="I33" si="21">-I649</f>
         <v>0</v>
       </c>
       <c r="J33" s="236">
@@ -10359,11 +10362,11 @@
         <v>0</v>
       </c>
       <c r="K33" s="236">
-        <f t="shared" ref="K33:L33" si="23">-K649</f>
+        <f t="shared" ref="K33:L33" si="22">-K649</f>
         <v>0</v>
       </c>
       <c r="L33" s="236">
-        <f t="shared" si="23"/>
+        <f t="shared" si="22"/>
         <v>0</v>
       </c>
     </row>
@@ -10376,31 +10379,31 @@
       <c r="D34" s="185"/>
       <c r="E34" s="185"/>
       <c r="F34" s="264">
-        <f t="shared" ref="F34:L34" si="24">F31+F33</f>
+        <f t="shared" ref="F34:L34" si="23">F31+F33</f>
         <v>-338700000</v>
       </c>
       <c r="G34" s="264">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-298400000</v>
       </c>
       <c r="H34" s="208">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-165041562.09016538</v>
       </c>
       <c r="I34" s="208">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-182239030.44808081</v>
       </c>
       <c r="J34" s="208">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-193316137.6387279</v>
       </c>
       <c r="K34" s="208">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-203235424.54314363</v>
       </c>
       <c r="L34" s="208">
-        <f t="shared" si="24"/>
+        <f t="shared" si="23"/>
         <v>-206177531.09173626</v>
       </c>
     </row>
@@ -10413,31 +10416,31 @@
       <c r="D35" s="276"/>
       <c r="E35" s="276"/>
       <c r="F35" s="287">
-        <f t="shared" ref="F35:L35" si="25">F34/F10</f>
+        <f t="shared" ref="F35:L35" si="24">F34/F10</f>
         <v>-0.11655998348131323</v>
       </c>
       <c r="G35" s="287">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-0.12042941318911939</v>
       </c>
       <c r="H35" s="287">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-6.6842066792635393E-2</v>
       </c>
       <c r="I35" s="287">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-7.3621737717650973E-2</v>
       </c>
       <c r="J35" s="287">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-7.5667753023877404E-2</v>
       </c>
       <c r="K35" s="287">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-7.5947331002497898E-2</v>
       </c>
       <c r="L35" s="287">
-        <f t="shared" si="25"/>
+        <f t="shared" si="24"/>
         <v>-7.2520481549521787E-2</v>
       </c>
     </row>
@@ -10476,19 +10479,19 @@
         <v>-138.3416279045812</v>
       </c>
       <c r="I37" s="178">
-        <f t="shared" ref="I37:L37" si="26">I34/I38*100</f>
+        <f t="shared" ref="I37:L37" si="25">I34/I38*100</f>
         <v>-152.75694086176094</v>
       </c>
       <c r="J37" s="178">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-162.04202652030838</v>
       </c>
       <c r="K37" s="178">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-170.35660062292007</v>
       </c>
       <c r="L37" s="178">
-        <f t="shared" si="26"/>
+        <f t="shared" si="25"/>
         <v>-172.82274190422152</v>
       </c>
     </row>
@@ -10513,19 +10516,19 @@
         <v>119300000</v>
       </c>
       <c r="I38" s="283">
-        <f t="shared" ref="I38:L38" si="27">H38</f>
+        <f t="shared" ref="I38:L38" si="26">H38</f>
         <v>119300000</v>
       </c>
       <c r="J38" s="283">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>119300000</v>
       </c>
       <c r="K38" s="283">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>119300000</v>
       </c>
       <c r="L38" s="283">
-        <f t="shared" si="27"/>
+        <f t="shared" si="26"/>
         <v>119300000</v>
       </c>
     </row>
@@ -10656,19 +10659,19 @@
         <v>2026</v>
       </c>
       <c r="I46" s="54">
-        <f t="shared" ref="I46" si="28">H46+1</f>
+        <f t="shared" ref="I46" si="27">H46+1</f>
         <v>2027</v>
       </c>
       <c r="J46" s="54">
-        <f t="shared" ref="J46" si="29">I46+1</f>
+        <f t="shared" ref="J46" si="28">I46+1</f>
         <v>2028</v>
       </c>
       <c r="K46" s="54">
-        <f t="shared" ref="K46" si="30">J46+1</f>
+        <f t="shared" ref="K46" si="29">J46+1</f>
         <v>2029</v>
       </c>
       <c r="L46" s="54">
-        <f t="shared" ref="L46" si="31">K46+1</f>
+        <f t="shared" ref="L46" si="30">K46+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -10755,19 +10758,19 @@
         <v>325616389.75624496</v>
       </c>
       <c r="I51" s="236">
-        <f t="shared" ref="I51:L51" si="32">I255</f>
+        <f t="shared" ref="I51:L51" si="31">I255</f>
         <v>325221703.22320706</v>
       </c>
       <c r="J51" s="236">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>334978354.31990337</v>
       </c>
       <c r="K51" s="236">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>350418762.8393364</v>
       </c>
       <c r="L51" s="236">
-        <f t="shared" si="32"/>
+        <f t="shared" si="31"/>
         <v>372036904.97757846</v>
       </c>
     </row>
@@ -10790,19 +10793,19 @@
         <v>0</v>
       </c>
       <c r="I52" s="184">
-        <f t="shared" ref="I52:L52" si="33">H52</f>
+        <f t="shared" ref="I52:L52" si="32">H52</f>
         <v>0</v>
       </c>
       <c r="J52" s="184">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="K52" s="184">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="L52" s="184">
-        <f t="shared" si="33"/>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
     </row>
@@ -10825,19 +10828,19 @@
         <v>49382543.062941171</v>
       </c>
       <c r="I53" s="236">
-        <f t="shared" ref="I53:L53" si="34">I344</f>
+        <f t="shared" ref="I53:L53" si="33">I344</f>
         <v>49506853.84444236</v>
       </c>
       <c r="J53" s="236">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>51096042.8751534</v>
       </c>
       <c r="K53" s="236">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>53520096.588110313</v>
       </c>
       <c r="L53" s="236">
-        <f t="shared" si="34"/>
+        <f t="shared" si="33"/>
         <v>56860496.975863181</v>
       </c>
     </row>
@@ -10860,19 +10863,19 @@
         <v>1200000</v>
       </c>
       <c r="I54" s="181">
-        <f t="shared" ref="I54:L54" si="35">H54</f>
+        <f t="shared" ref="I54:L54" si="34">H54</f>
         <v>1200000</v>
       </c>
       <c r="J54" s="181">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1200000</v>
       </c>
       <c r="K54" s="181">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1200000</v>
       </c>
       <c r="L54" s="181">
-        <f t="shared" si="35"/>
+        <f t="shared" si="34"/>
         <v>1200000</v>
       </c>
       <c r="N54" t="s">
@@ -10898,11 +10901,11 @@
         <v>120299905.56847787</v>
       </c>
       <c r="I55" s="181">
-        <f t="shared" ref="I55:L55" si="36">I143</f>
+        <f t="shared" ref="I55:L55" si="35">I143</f>
         <v>30000000.000000015</v>
       </c>
       <c r="J55" s="181">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>30000000.000000015</v>
       </c>
       <c r="K55" s="181">
@@ -10910,7 +10913,7 @@
         <v>30000000.000000015</v>
       </c>
       <c r="L55" s="181">
-        <f t="shared" si="36"/>
+        <f t="shared" si="35"/>
         <v>30000000.000000015</v>
       </c>
     </row>
@@ -10933,19 +10936,19 @@
         <v>3700000</v>
       </c>
       <c r="I56" s="181">
-        <f t="shared" ref="I56:L56" si="37">I658</f>
+        <f t="shared" ref="I56:L56" si="36">I658</f>
         <v>3700000</v>
       </c>
       <c r="J56" s="181">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>3700000</v>
       </c>
       <c r="K56" s="181">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>3700000</v>
       </c>
       <c r="L56" s="181">
-        <f t="shared" si="37"/>
+        <f t="shared" si="36"/>
         <v>3700000</v>
       </c>
     </row>
@@ -10962,27 +10965,27 @@
         <v>1146400000</v>
       </c>
       <c r="G57" s="355">
-        <f t="shared" ref="G57:L57" si="38">SUM(G51:G56)</f>
+        <f t="shared" ref="G57:L57" si="37">SUM(G51:G56)</f>
         <v>775300000</v>
       </c>
       <c r="H57" s="229">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>500198838.38766402</v>
       </c>
       <c r="I57" s="229">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>409628557.06764942</v>
       </c>
       <c r="J57" s="229">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>420974397.1950568</v>
       </c>
       <c r="K57" s="229">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>438838859.42744672</v>
       </c>
       <c r="L57" s="229">
-        <f t="shared" si="38"/>
+        <f t="shared" si="37"/>
         <v>463797401.95344162</v>
       </c>
     </row>
@@ -11019,19 +11022,19 @@
         <v>140497715.50265881</v>
       </c>
       <c r="I59" s="181">
-        <f t="shared" ref="I59:L59" si="39">I451</f>
+        <f t="shared" ref="I59:L59" si="38">I451</f>
         <v>123689579.44162276</v>
       </c>
       <c r="J59" s="181">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>103493003.12408732</v>
       </c>
       <c r="K59" s="181">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>80081402.713204086</v>
       </c>
       <c r="L59" s="181">
-        <f t="shared" si="39"/>
+        <f t="shared" si="38"/>
         <v>53590738.714863062</v>
       </c>
     </row>
@@ -11054,19 +11057,19 @@
         <v>460418533.51363516</v>
       </c>
       <c r="I60" s="181">
-        <f t="shared" ref="I60:L60" si="40">I481</f>
+        <f t="shared" ref="I60:L60" si="39">I481</f>
         <v>430882554.97087586</v>
       </c>
       <c r="J60" s="181">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>387158559.77577114</v>
       </c>
       <c r="K60" s="181">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>329972672.9960013</v>
       </c>
       <c r="L60" s="181">
-        <f t="shared" si="40"/>
+        <f t="shared" si="39"/>
         <v>259894186.03870523</v>
       </c>
     </row>
@@ -11089,19 +11092,19 @@
         <v>154890000</v>
       </c>
       <c r="I61" s="181">
-        <f t="shared" ref="I61:L61" si="41">I401</f>
+        <f t="shared" ref="I61:L61" si="40">I401</f>
         <v>137680000</v>
       </c>
       <c r="J61" s="181">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>120470000</v>
       </c>
       <c r="K61" s="181">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>103260000</v>
       </c>
       <c r="L61" s="181">
-        <f t="shared" si="41"/>
+        <f t="shared" si="40"/>
         <v>86050000</v>
       </c>
     </row>
@@ -11124,19 +11127,19 @@
         <v>6200000</v>
       </c>
       <c r="I62" s="181">
-        <f t="shared" ref="I62:L62" si="42">H62</f>
+        <f t="shared" ref="I62:L62" si="41">H62</f>
         <v>6200000</v>
       </c>
       <c r="J62" s="181">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>6200000</v>
       </c>
       <c r="K62" s="181">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>6200000</v>
       </c>
       <c r="L62" s="181">
-        <f t="shared" si="42"/>
+        <f t="shared" si="41"/>
         <v>6200000</v>
       </c>
     </row>
@@ -11159,19 +11162,19 @@
         <v>44900000</v>
       </c>
       <c r="I63" s="181">
-        <f t="shared" ref="I63:L63" si="43">H63</f>
+        <f t="shared" ref="I63:L63" si="42">H63</f>
         <v>44900000</v>
       </c>
       <c r="J63" s="181">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>44900000</v>
       </c>
       <c r="K63" s="181">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>44900000</v>
       </c>
       <c r="L63" s="181">
-        <f t="shared" si="43"/>
+        <f t="shared" si="42"/>
         <v>44900000</v>
       </c>
     </row>
@@ -11194,19 +11197,19 @@
         <v>1800000</v>
       </c>
       <c r="I64" s="181">
-        <f t="shared" ref="I64:L64" si="44">H64</f>
+        <f t="shared" ref="I64:L64" si="43">H64</f>
         <v>1800000</v>
       </c>
       <c r="J64" s="181">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1800000</v>
       </c>
       <c r="K64" s="181">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1800000</v>
       </c>
       <c r="L64" s="181">
-        <f t="shared" si="44"/>
+        <f t="shared" si="43"/>
         <v>1800000</v>
       </c>
       <c r="N64" t="s">
@@ -11232,19 +11235,19 @@
         <v>100000</v>
       </c>
       <c r="I65" s="181">
-        <f t="shared" ref="I65:L65" si="45">H65</f>
+        <f t="shared" ref="I65:L65" si="44">H65</f>
         <v>100000</v>
       </c>
       <c r="J65" s="181">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>100000</v>
       </c>
       <c r="K65" s="181">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>100000</v>
       </c>
       <c r="L65" s="181">
-        <f t="shared" si="45"/>
+        <f t="shared" si="44"/>
         <v>100000</v>
       </c>
       <c r="N65" t="s">
@@ -11270,19 +11273,19 @@
         <v>44700000</v>
       </c>
       <c r="I66" s="181">
-        <f t="shared" ref="I66:L66" si="46">I672</f>
+        <f t="shared" ref="I66:L66" si="45">I672</f>
         <v>44700000</v>
       </c>
       <c r="J66" s="181">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>44700000</v>
       </c>
       <c r="K66" s="181">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>44700000</v>
       </c>
       <c r="L66" s="181">
-        <f t="shared" si="46"/>
+        <f t="shared" si="45"/>
         <v>44700000</v>
       </c>
     </row>
@@ -11386,19 +11389,19 @@
         <v>-594249911.30514705</v>
       </c>
       <c r="I71" s="181">
-        <f t="shared" ref="I71:L71" si="47">-I348</f>
+        <f t="shared" ref="I71:L71" si="46">-I348</f>
         <v>-593529608.38235295</v>
       </c>
       <c r="J71" s="181">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>-611335496.63382375</v>
       </c>
       <c r="K71" s="181">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>-639514242.18178904</v>
       </c>
       <c r="L71" s="181">
-        <f t="shared" si="47"/>
+        <f t="shared" si="46"/>
         <v>-678967351.58408082</v>
       </c>
     </row>
@@ -11421,19 +11424,19 @@
         <v>-9800000</v>
       </c>
       <c r="I72" s="181">
-        <f t="shared" ref="I72:L72" si="48">H72</f>
+        <f t="shared" ref="I72:L72" si="47">H72</f>
         <v>-9800000</v>
       </c>
       <c r="J72" s="181">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-9800000</v>
       </c>
       <c r="K72" s="181">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-9800000</v>
       </c>
       <c r="L72" s="181">
-        <f t="shared" si="48"/>
+        <f t="shared" si="47"/>
         <v>-9800000</v>
       </c>
     </row>
@@ -11456,19 +11459,19 @@
         <v>-26125950</v>
       </c>
       <c r="I73" s="181">
-        <f t="shared" ref="I73:L73" si="49">I416</f>
+        <f t="shared" ref="I73:L73" si="48">I416</f>
         <v>-26909728.5</v>
       </c>
       <c r="J73" s="181">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>-27717020.355</v>
       </c>
       <c r="K73" s="181">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>-28548530.96565</v>
       </c>
       <c r="L73" s="181">
-        <f t="shared" si="49"/>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
     </row>
@@ -11491,19 +11494,19 @@
         <v>-3580348.8065704112</v>
       </c>
       <c r="I74" s="181">
-        <f t="shared" ref="I74:L74" si="50">I329</f>
+        <f t="shared" ref="I74:L74" si="49">I329</f>
         <v>-3323649.9067753511</v>
       </c>
       <c r="J74" s="181">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>-3066951.0069802916</v>
       </c>
       <c r="K74" s="181">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>-2810252.107185232</v>
       </c>
       <c r="L74" s="181">
-        <f t="shared" si="50"/>
+        <f t="shared" si="49"/>
         <v>-2553553.2073901719</v>
       </c>
     </row>
@@ -11559,23 +11562,23 @@
         <v>-661000000</v>
       </c>
       <c r="H76" s="229">
-        <f t="shared" ref="H76:L76" si="51">SUM(H71:H75)</f>
+        <f t="shared" ref="H76:L76" si="50">SUM(H71:H75)</f>
         <v>-633756210.11171746</v>
       </c>
       <c r="I76" s="229">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>-633562986.7891283</v>
       </c>
       <c r="J76" s="229">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>-651919467.99580407</v>
       </c>
       <c r="K76" s="229">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>-680673025.25462425</v>
       </c>
       <c r="L76" s="229">
-        <f t="shared" si="51"/>
+        <f t="shared" si="50"/>
         <v>-691320904.791471</v>
       </c>
     </row>
@@ -11646,7 +11649,7 @@
         <v>-688100000</v>
       </c>
       <c r="G80" s="356">
-        <f t="shared" ref="G80" si="52">SUM(G78,G79)</f>
+        <f t="shared" ref="G80" si="51">SUM(G78,G79)</f>
         <v>-503600000</v>
       </c>
       <c r="H80" s="246">
@@ -11703,19 +11706,19 @@
         <v>-79581389.382405967</v>
       </c>
       <c r="I82" s="181">
-        <f t="shared" ref="I82:L82" si="53">I330</f>
+        <f t="shared" ref="I82:L82" si="52">I330</f>
         <v>-73875672.927870303</v>
       </c>
       <c r="J82" s="181">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>-68169956.47333467</v>
       </c>
       <c r="K82" s="181">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>-62464240.018799022</v>
       </c>
       <c r="L82" s="181">
-        <f t="shared" si="53"/>
+        <f t="shared" si="52"/>
         <v>-56758523.564263366</v>
       </c>
     </row>
@@ -11738,19 +11741,19 @@
         <v>-300000</v>
       </c>
       <c r="I83" s="181">
-        <f t="shared" ref="I83:L83" si="54">H83</f>
+        <f t="shared" ref="I83:L83" si="53">H83</f>
         <v>-300000</v>
       </c>
       <c r="J83" s="181">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>-300000</v>
       </c>
       <c r="K83" s="181">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>-300000</v>
       </c>
       <c r="L83" s="181">
-        <f t="shared" si="54"/>
+        <f t="shared" si="53"/>
         <v>-300000</v>
       </c>
     </row>
@@ -11773,19 +11776,19 @@
         <v>-173009050</v>
       </c>
       <c r="I84" s="181">
-        <f t="shared" ref="I84:L84" si="55">I417</f>
+        <f t="shared" ref="I84:L84" si="54">I417</f>
         <v>-146099321.5</v>
       </c>
       <c r="J84" s="181">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>-118382301.145</v>
       </c>
       <c r="K84" s="181">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>-89833770.179350019</v>
       </c>
       <c r="L84" s="181">
-        <f t="shared" si="55"/>
+        <f t="shared" si="54"/>
         <v>-89833770.179350019</v>
       </c>
     </row>
@@ -11802,7 +11805,7 @@
         <v>-1037500000</v>
       </c>
       <c r="G85" s="355">
-        <f t="shared" ref="G85:L85" si="56">SUM(G80:G84)</f>
+        <f t="shared" ref="G85:L85" si="55">SUM(G80:G84)</f>
         <v>-798700000</v>
       </c>
       <c r="H85" s="229">
@@ -11810,19 +11813,19 @@
         <v>-672590439.382406</v>
       </c>
       <c r="I85" s="229">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>-700898297.22926605</v>
       </c>
       <c r="J85" s="229">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>-806073222.27608538</v>
       </c>
       <c r="K85" s="229">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>-900612064.60214567</v>
       </c>
       <c r="L85" s="229">
-        <f t="shared" si="56"/>
+        <f t="shared" si="55"/>
         <v>-1007321107.7273929</v>
       </c>
     </row>
@@ -11853,27 +11856,27 @@
         <v>-1749900000</v>
       </c>
       <c r="G87" s="263">
-        <f t="shared" ref="G87:L87" si="57">G85+G76</f>
+        <f t="shared" ref="G87:L87" si="56">G85+G76</f>
         <v>-1459700000</v>
       </c>
       <c r="H87" s="212">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-1306346649.4941235</v>
       </c>
       <c r="I87" s="212">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-1334461284.0183945</v>
       </c>
       <c r="J87" s="212">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-1457992690.2718894</v>
       </c>
       <c r="K87" s="212">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-1581285089.85677</v>
       </c>
       <c r="L87" s="212">
-        <f t="shared" si="57"/>
+        <f t="shared" si="56"/>
         <v>-1698642012.5188639</v>
       </c>
     </row>
@@ -11910,19 +11913,19 @@
         <v>4200000</v>
       </c>
       <c r="I89" s="181">
-        <f t="shared" ref="I89:L89" si="58">H89</f>
+        <f t="shared" ref="I89:L89" si="57">H89</f>
         <v>4200000</v>
       </c>
       <c r="J89" s="181">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>4200000</v>
       </c>
       <c r="K89" s="181">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>4200000</v>
       </c>
       <c r="L89" s="181">
-        <f t="shared" si="58"/>
+        <f t="shared" si="57"/>
         <v>4200000</v>
       </c>
     </row>
@@ -11941,23 +11944,23 @@
         <v>322600000</v>
       </c>
       <c r="H90" s="236">
-        <f t="shared" ref="H90:L90" si="59">G90</f>
+        <f t="shared" ref="H90:L90" si="58">G90</f>
         <v>322600000</v>
       </c>
       <c r="I90" s="181">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>322600000</v>
       </c>
       <c r="J90" s="181">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>322600000</v>
       </c>
       <c r="K90" s="181">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>322600000</v>
       </c>
       <c r="L90" s="181">
-        <f t="shared" si="59"/>
+        <f t="shared" si="58"/>
         <v>322600000</v>
       </c>
     </row>
@@ -11976,23 +11979,23 @@
         <v>3600000</v>
       </c>
       <c r="H91" s="181">
-        <f t="shared" ref="H91:L91" si="60">G91</f>
+        <f t="shared" ref="H91:L91" si="59">G91</f>
         <v>3600000</v>
       </c>
       <c r="I91" s="181">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>3600000</v>
       </c>
       <c r="J91" s="181">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>3600000</v>
       </c>
       <c r="K91" s="181">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>3600000</v>
       </c>
       <c r="L91" s="181">
-        <f t="shared" si="60"/>
+        <f t="shared" si="59"/>
         <v>3600000</v>
       </c>
     </row>
@@ -12015,19 +12018,19 @@
         <v>-283041562.09016538</v>
       </c>
       <c r="I92" s="181">
-        <f t="shared" ref="I92:L92" si="61">I697</f>
+        <f t="shared" ref="I92:L92" si="60">I697</f>
         <v>-465280592.53824615</v>
       </c>
       <c r="J92" s="181">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-658596730.17697406</v>
       </c>
       <c r="K92" s="181">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-861832154.72011769</v>
       </c>
       <c r="L92" s="181">
-        <f t="shared" si="61"/>
+        <f t="shared" si="60"/>
         <v>-1068009685.8118539</v>
       </c>
     </row>
@@ -12044,7 +12047,7 @@
         <v>2271200000</v>
       </c>
       <c r="G93" s="355">
-        <f t="shared" ref="G93" si="62">SUM(G89:G92)-G87</f>
+        <f t="shared" ref="G93" si="61">SUM(G89:G92)-G87</f>
         <v>1672100000</v>
       </c>
       <c r="H93" s="229">
@@ -12056,15 +12059,15 @@
         <v>1199580691.4801483</v>
       </c>
       <c r="J93" s="229">
-        <f t="shared" ref="J93:L93" si="63">SUM(J89:J92)-J87</f>
+        <f t="shared" ref="J93:L93" si="62">SUM(J89:J92)-J87</f>
         <v>1129795960.0949154</v>
       </c>
       <c r="K93" s="229">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>1049852935.1366524</v>
       </c>
       <c r="L93" s="229">
-        <f t="shared" si="63"/>
+        <f t="shared" si="62"/>
         <v>961032326.70701003</v>
       </c>
     </row>
@@ -12075,11 +12078,11 @@
       <c r="D94" s="61"/>
       <c r="E94" s="61"/>
       <c r="F94" s="181">
-        <f t="shared" ref="F94:L94" si="64">F67-F93</f>
+        <f t="shared" ref="F94:L94" si="63">F67-F93</f>
         <v>0</v>
       </c>
       <c r="G94" s="181">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="H94" s="181">
@@ -12087,19 +12090,19 @@
         <v>0</v>
       </c>
       <c r="I94" s="181">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="J94" s="181">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="K94" s="181">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
       <c r="L94" s="181">
-        <f t="shared" si="64"/>
+        <f t="shared" si="63"/>
         <v>0</v>
       </c>
     </row>
@@ -12272,19 +12275,19 @@
         <v>2026</v>
       </c>
       <c r="I105" s="54">
-        <f t="shared" ref="I105" si="65">H105+1</f>
+        <f t="shared" ref="I105" si="64">H105+1</f>
         <v>2027</v>
       </c>
       <c r="J105" s="54">
-        <f t="shared" ref="J105" si="66">I105+1</f>
+        <f t="shared" ref="J105" si="65">I105+1</f>
         <v>2028</v>
       </c>
       <c r="K105" s="54">
-        <f t="shared" ref="K105" si="67">J105+1</f>
+        <f t="shared" ref="K105" si="66">J105+1</f>
         <v>2029</v>
       </c>
       <c r="L105" s="54">
-        <f t="shared" ref="L105" si="68">K105+1</f>
+        <f t="shared" ref="L105" si="67">K105+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -12398,19 +12401,19 @@
         <v>32655301.722517647</v>
       </c>
       <c r="I111" s="181">
-        <f t="shared" ref="I111:L111" si="69">I442</f>
+        <f t="shared" ref="I111:L111" si="68">I442</f>
         <v>36610877.59881299</v>
       </c>
       <c r="J111" s="181">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>40634993.467596814</v>
       </c>
       <c r="K111" s="181">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>44819639.046127364</v>
       </c>
       <c r="L111" s="181">
-        <f t="shared" si="69"/>
+        <f t="shared" si="68"/>
         <v>49234862.788686305</v>
       </c>
     </row>
@@ -12429,19 +12432,19 @@
         <v>17210000</v>
       </c>
       <c r="I112" s="181">
-        <f t="shared" ref="I112:L112" si="70">I395</f>
+        <f t="shared" ref="I112:L112" si="69">I395</f>
         <v>17210000</v>
       </c>
       <c r="J112" s="181">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>17210000</v>
       </c>
       <c r="K112" s="181">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>17210000</v>
       </c>
       <c r="L112" s="181">
-        <f t="shared" si="70"/>
+        <f t="shared" si="69"/>
         <v>17210000</v>
       </c>
     </row>
@@ -12460,19 +12463,19 @@
         <v>95890948.168181688</v>
       </c>
       <c r="I113" s="181">
-        <f t="shared" ref="I113:L113" si="71">I469</f>
+        <f t="shared" ref="I113:L113" si="70">I469</f>
         <v>112453664.98009716</v>
       </c>
       <c r="J113" s="181">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>129303371.22702277</v>
       </c>
       <c r="K113" s="181">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>146825244.61359733</v>
       </c>
       <c r="L113" s="181">
-        <f t="shared" si="71"/>
+        <f t="shared" si="70"/>
         <v>165312590.77916718</v>
       </c>
     </row>
@@ -12491,19 +12494,19 @@
         <v>51450978.485960901</v>
       </c>
       <c r="I114" s="181">
-        <f t="shared" ref="I114:L114" si="72">-I352</f>
+        <f t="shared" ref="I114:L114" si="71">-I352</f>
         <v>-449927.17125737667</v>
       </c>
       <c r="J114" s="181">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>6460048.1240634322</v>
       </c>
       <c r="K114" s="181">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>10314283.315575361</v>
       </c>
       <c r="L114" s="181">
-        <f t="shared" si="72"/>
+        <f t="shared" si="71"/>
         <v>14494566.876296878</v>
       </c>
     </row>
@@ -12553,19 +12556,19 @@
         <v>0</v>
       </c>
       <c r="I116" s="184">
-        <f t="shared" ref="I116:L116" si="73">-I652</f>
+        <f t="shared" ref="I116:L116" si="72">-I652</f>
         <v>0</v>
       </c>
       <c r="J116" s="184">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="K116" s="184">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
       <c r="L116" s="184">
-        <f t="shared" si="73"/>
+        <f t="shared" si="72"/>
         <v>0</v>
       </c>
     </row>
@@ -12720,19 +12723,19 @@
         <v>-19753017.225176468</v>
       </c>
       <c r="I124" s="181">
-        <f t="shared" ref="I124:L124" si="74">-I428</f>
+        <f t="shared" ref="I124:L124" si="73">-I428</f>
         <v>-19802741.537776943</v>
       </c>
       <c r="J124" s="181">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>-20438417.150061361</v>
       </c>
       <c r="K124" s="181">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>-21408038.635244127</v>
       </c>
       <c r="L124" s="181">
-        <f t="shared" si="74"/>
+        <f t="shared" si="73"/>
         <v>-22744198.790345274</v>
       </c>
     </row>
@@ -12751,19 +12754,19 @@
         <v>-82709481.681816876</v>
       </c>
       <c r="I125" s="181">
-        <f t="shared" ref="I125:L125" si="75">-I455</f>
+        <f t="shared" ref="I125:L125" si="74">-I455</f>
         <v>-82917686.437337875</v>
       </c>
       <c r="J125" s="181">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>-85579376.031918079</v>
       </c>
       <c r="K125" s="181">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>-89639357.83382751</v>
       </c>
       <c r="L125" s="181">
-        <f t="shared" si="75"/>
+        <f t="shared" si="74"/>
         <v>-95234103.821871102</v>
       </c>
     </row>
@@ -12796,19 +12799,19 @@
         <v>-102462498.90699334</v>
       </c>
       <c r="I127" s="229">
-        <f t="shared" ref="I127:L127" si="76">I124+I125</f>
+        <f t="shared" ref="I127:L127" si="75">I124+I125</f>
         <v>-102720427.97511482</v>
       </c>
       <c r="J127" s="229">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>-106017793.18197945</v>
       </c>
       <c r="K127" s="229">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>-111047396.46907164</v>
       </c>
       <c r="L127" s="229">
-        <f t="shared" si="76"/>
+        <f t="shared" si="75"/>
         <v>-117978302.61221638</v>
       </c>
     </row>
@@ -12871,19 +12874,19 @@
         <v>150000000</v>
       </c>
       <c r="I131" s="181">
-        <f t="shared" ref="I131:L131" si="77">I557</f>
+        <f t="shared" ref="I131:L131" si="76">I557</f>
         <v>60923302.801395714</v>
       </c>
       <c r="J131" s="181">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>138597661.85635501</v>
       </c>
       <c r="K131" s="181">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>398493089.74624586</v>
       </c>
       <c r="L131" s="181">
-        <f t="shared" si="77"/>
+        <f t="shared" si="76"/>
         <v>112414759.57978298</v>
       </c>
     </row>
@@ -12902,19 +12905,19 @@
         <v>-233900000</v>
       </c>
       <c r="I132" s="181">
-        <f t="shared" ref="I132:L132" si="78">I558</f>
+        <f t="shared" ref="I132:L132" si="77">I558</f>
         <v>0</v>
       </c>
       <c r="J132" s="181">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
       <c r="K132" s="181">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>-269700000</v>
       </c>
       <c r="L132" s="181">
-        <f t="shared" si="78"/>
+        <f t="shared" si="77"/>
         <v>0</v>
       </c>
     </row>
@@ -12933,19 +12936,19 @@
         <v>-25365000</v>
       </c>
       <c r="I133" s="181">
-        <f t="shared" ref="I133:L133" si="79">-I415</f>
+        <f t="shared" ref="I133:L133" si="78">-I415</f>
         <v>-26125950</v>
       </c>
       <c r="J133" s="181">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-26909728.5</v>
       </c>
       <c r="K133" s="181">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-27717020.355</v>
       </c>
       <c r="L133" s="181">
-        <f t="shared" si="79"/>
+        <f t="shared" si="78"/>
         <v>-28548530.96565</v>
       </c>
     </row>
@@ -12964,19 +12967,19 @@
         <v>0</v>
       </c>
       <c r="I134" s="186">
-        <f t="shared" ref="I134:L134" si="80">-I688</f>
+        <f t="shared" ref="I134:L134" si="79">-I688</f>
         <v>0</v>
       </c>
       <c r="J134" s="186">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="K134" s="186">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
       <c r="L134" s="186">
-        <f t="shared" si="80"/>
+        <f t="shared" si="79"/>
         <v>0</v>
       </c>
     </row>
@@ -12995,19 +12998,19 @@
         <v>0</v>
       </c>
       <c r="I135" s="186">
-        <f t="shared" ref="I135:L135" si="81">I695</f>
+        <f t="shared" ref="I135:L135" si="80">I695</f>
         <v>0</v>
       </c>
       <c r="J135" s="186">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="K135" s="186">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
       <c r="L135" s="186">
-        <f t="shared" si="81"/>
+        <f t="shared" si="80"/>
         <v>0</v>
       </c>
     </row>
@@ -13040,19 +13043,19 @@
         <v>-109265000</v>
       </c>
       <c r="I137" s="229">
-        <f t="shared" ref="I137:L137" si="82">SUM(I131:I135)</f>
+        <f t="shared" ref="I137:L137" si="81">SUM(I131:I135)</f>
         <v>34797352.801395714</v>
       </c>
       <c r="J137" s="229">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>111687933.35635501</v>
       </c>
       <c r="K137" s="229">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>101076069.39124586</v>
       </c>
       <c r="L137" s="229">
-        <f t="shared" si="82"/>
+        <f t="shared" si="81"/>
         <v>83866228.614132971</v>
       </c>
     </row>
@@ -13119,15 +13122,15 @@
         <v>120299905.56847787</v>
       </c>
       <c r="J141" s="223">
-        <f t="shared" ref="J141:L141" si="83">I143</f>
+        <f t="shared" ref="J141:L141" si="82">I143</f>
         <v>30000000.000000015</v>
       </c>
       <c r="K141" s="223">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>30000000.000000015</v>
       </c>
       <c r="L141" s="223">
-        <f t="shared" si="83"/>
+        <f t="shared" si="82"/>
         <v>30000000.000000015</v>
       </c>
     </row>
@@ -13146,19 +13149,19 @@
         <v>-198600094.43152213</v>
       </c>
       <c r="I142" s="247">
-        <f t="shared" ref="I142:L142" si="84">I120+I127+I137</f>
+        <f t="shared" ref="I142:L142" si="83">I120+I127+I137</f>
         <v>-90299905.568477854</v>
       </c>
       <c r="J142" s="247">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="K142" s="247">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
       <c r="L142" s="247">
-        <f t="shared" si="84"/>
+        <f t="shared" si="83"/>
         <v>0</v>
       </c>
     </row>
@@ -13177,19 +13180,19 @@
         <v>120299905.56847787</v>
       </c>
       <c r="I143" s="223">
-        <f t="shared" ref="I143:L143" si="85">SUM(I141:I142)</f>
+        <f t="shared" ref="I143:L143" si="84">SUM(I141:I142)</f>
         <v>30000000.000000015</v>
       </c>
       <c r="J143" s="223">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>30000000.000000015</v>
       </c>
       <c r="K143" s="223">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>30000000.000000015</v>
       </c>
       <c r="L143" s="223">
-        <f t="shared" si="85"/>
+        <f t="shared" si="84"/>
         <v>30000000.000000015</v>
       </c>
     </row>
@@ -13334,19 +13337,19 @@
         <v>2026</v>
       </c>
       <c r="I152" s="54">
-        <f t="shared" ref="I152" si="86">H152+1</f>
+        <f t="shared" ref="I152" si="85">H152+1</f>
         <v>2027</v>
       </c>
       <c r="J152" s="54">
-        <f t="shared" ref="J152" si="87">I152+1</f>
+        <f t="shared" ref="J152" si="86">I152+1</f>
         <v>2028</v>
       </c>
       <c r="K152" s="54">
-        <f t="shared" ref="K152" si="88">J152+1</f>
+        <f t="shared" ref="K152" si="87">J152+1</f>
         <v>2029</v>
       </c>
       <c r="L152" s="54">
-        <f t="shared" ref="L152" si="89">K152+1</f>
+        <f t="shared" ref="L152" si="88">K152+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -13427,27 +13430,27 @@
         <v>19700000</v>
       </c>
       <c r="G157" s="322">
-        <f t="shared" ref="G157:L157" si="90">G196</f>
+        <f t="shared" ref="G157:L157" si="89">G196</f>
         <v>17000000</v>
       </c>
       <c r="H157" s="322">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>16500000</v>
       </c>
       <c r="I157" s="322">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>16000000</v>
       </c>
       <c r="J157" s="322">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>16000000</v>
       </c>
       <c r="K157" s="322">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>16250000</v>
       </c>
       <c r="L157" s="322">
-        <f t="shared" si="90"/>
+        <f t="shared" si="89"/>
         <v>16750000</v>
       </c>
     </row>
@@ -13464,27 +13467,27 @@
         <v>68000000</v>
       </c>
       <c r="G158" s="322">
-        <f t="shared" ref="G158:L158" si="91">G199</f>
+        <f t="shared" ref="G158:L158" si="90">G199</f>
         <v>57000000</v>
       </c>
       <c r="H158" s="322">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>55323529.411764704</v>
       </c>
       <c r="I158" s="322">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>53647058.823529415</v>
       </c>
       <c r="J158" s="322">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>53647058.823529415</v>
       </c>
       <c r="K158" s="322">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>54485294.117647059</v>
       </c>
       <c r="L158" s="322">
-        <f t="shared" si="91"/>
+        <f t="shared" si="90"/>
         <v>56161764.705882356</v>
       </c>
     </row>
@@ -13501,27 +13504,27 @@
         <v>2917800000</v>
       </c>
       <c r="G159" s="236">
-        <f t="shared" ref="G159:L159" si="92">G203</f>
+        <f t="shared" ref="G159:L159" si="91">G203</f>
         <v>2456300000</v>
       </c>
       <c r="H159" s="236">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>2453502266.4705882</v>
       </c>
       <c r="I159" s="236">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>2460044939.1811767</v>
       </c>
       <c r="J159" s="236">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>2543686467.113337</v>
       </c>
       <c r="K159" s="236">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>2671268241.4794903</v>
       </c>
       <c r="L159" s="236">
-        <f t="shared" si="92"/>
+        <f t="shared" si="91"/>
         <v>2847078788.2033253</v>
       </c>
     </row>
@@ -13609,31 +13612,31 @@
       <c r="D164" s="51"/>
       <c r="E164" s="51"/>
       <c r="F164" s="346">
-        <f t="shared" ref="F164:L164" si="93">F13</f>
+        <f t="shared" ref="F164:L164" si="92">F13</f>
         <v>0.40006194507536652</v>
       </c>
       <c r="G164" s="346">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.47086124788118494</v>
       </c>
       <c r="H164" s="346">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.46517320634024412</v>
       </c>
       <c r="I164" s="346">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.46716279348372142</v>
       </c>
       <c r="J164" s="346">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.46824714815105417</v>
       </c>
       <c r="K164" s="346">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.46893116754214242</v>
       </c>
       <c r="L164" s="346">
-        <f t="shared" si="93"/>
+        <f t="shared" si="92"/>
         <v>0.46929189257913345</v>
       </c>
     </row>
@@ -13646,31 +13649,31 @@
       <c r="D165" s="51"/>
       <c r="E165" s="51"/>
       <c r="F165" s="346">
-        <f t="shared" ref="F165:L165" si="94">F19</f>
+        <f t="shared" ref="F165:L165" si="93">F19</f>
         <v>-0.11421983618968959</v>
       </c>
       <c r="G165" s="346">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-8.5680845911695863E-2</v>
       </c>
       <c r="H165" s="346">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-4.5842500231669456E-2</v>
       </c>
       <c r="I165" s="346">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-5.250322709341599E-2</v>
       </c>
       <c r="J165" s="346">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-5.2659127714179736E-2</v>
       </c>
       <c r="K165" s="346">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-4.8315656129789747E-2</v>
       </c>
       <c r="L165" s="346">
-        <f t="shared" si="94"/>
+        <f t="shared" si="93"/>
         <v>-4.1209072703621091E-2</v>
       </c>
     </row>
@@ -13683,31 +13686,31 @@
       <c r="D166" s="51"/>
       <c r="E166" s="51"/>
       <c r="F166" s="346">
-        <f t="shared" ref="F166:L166" si="95">F26</f>
-        <v>-0.17317089958015006</v>
+        <f t="shared" ref="F166:L166" si="94">F26</f>
+        <v>-5.5268772799229128E-2</v>
       </c>
       <c r="G166" s="346">
-        <f t="shared" si="95"/>
-        <v>-0.15275647752038099</v>
+        <f t="shared" si="94"/>
+        <v>-1.8605214303010736E-2</v>
       </c>
       <c r="H166" s="346">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>1.3188987759916469E-2</v>
       </c>
       <c r="I166" s="346">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>1.4669105489611249E-2</v>
       </c>
       <c r="J166" s="346">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>2.0594437205472667E-2</v>
       </c>
       <c r="K166" s="346">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>2.9731618435900255E-2</v>
       </c>
       <c r="L166" s="346">
-        <f t="shared" si="95"/>
+        <f t="shared" si="94"/>
         <v>4.0308840749099045E-2</v>
       </c>
     </row>
@@ -13720,31 +13723,31 @@
       <c r="D167" s="51"/>
       <c r="E167" s="51"/>
       <c r="F167" s="346">
-        <f t="shared" ref="F167:L167" si="96">F35</f>
+        <f t="shared" ref="F167:L167" si="95">F35</f>
         <v>-0.11655998348131323</v>
       </c>
       <c r="G167" s="346">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>-0.12042941318911939</v>
       </c>
       <c r="H167" s="346">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>-6.6842066792635393E-2</v>
       </c>
       <c r="I167" s="346">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>-7.3621737717650973E-2</v>
       </c>
       <c r="J167" s="346">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>-7.5667753023877404E-2</v>
       </c>
       <c r="K167" s="346">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>-7.5947331002497898E-2</v>
       </c>
       <c r="L167" s="346">
-        <f t="shared" si="96"/>
+        <f t="shared" si="95"/>
         <v>-7.2520481549521787E-2</v>
       </c>
     </row>
@@ -13802,27 +13805,27 @@
       <c r="E171" s="51"/>
       <c r="F171" s="346"/>
       <c r="G171" s="347">
-        <f t="shared" ref="G171:L171" si="97">IF(AVERAGE(SUM(H89:H92),SUM(G89:G92))&lt;0,"N/M",G34/AVERAGE(SUM(H89:H92),SUM(G89:G92)))</f>
+        <f t="shared" ref="G171:L171" si="96">IF(AVERAGE(SUM(H89:H92),SUM(G89:G92))&lt;0,"N/M",G34/AVERAGE(SUM(H89:H92),SUM(G89:G92)))</f>
         <v>-2.2975192059291514</v>
       </c>
       <c r="H171" s="347" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>N/M</v>
       </c>
       <c r="I171" s="347" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>N/M</v>
       </c>
       <c r="J171" s="347" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>N/M</v>
       </c>
       <c r="K171" s="347" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>N/M</v>
       </c>
       <c r="L171" s="347" t="str">
-        <f t="shared" si="97"/>
+        <f t="shared" si="96"/>
         <v>N/M</v>
       </c>
     </row>
@@ -13852,27 +13855,27 @@
       <c r="E173" s="51"/>
       <c r="F173" s="348"/>
       <c r="G173" s="346">
-        <f t="shared" ref="G173:L173" si="98">IF(AVERAGE(F67,G67)&lt;0, "N/M", G34/AVERAGE(F67,G67))</f>
+        <f t="shared" ref="G173:L173" si="97">IF(AVERAGE(F67,G67)&lt;0, "N/M", G34/AVERAGE(F67,G67))</f>
         <v>-0.15134531990972028</v>
       </c>
       <c r="H173" s="346">
-        <f t="shared" si="98"/>
+        <f t="shared" si="97"/>
         <v>-0.10908935461653654</v>
       </c>
       <c r="I173" s="346">
-        <f t="shared" si="98"/>
+        <f t="shared" si="97"/>
         <v>-0.14274863546823729</v>
       </c>
       <c r="J173" s="346">
-        <f t="shared" si="98"/>
+        <f t="shared" si="97"/>
         <v>-0.1659810039806251</v>
       </c>
       <c r="K173" s="346">
-        <f t="shared" si="98"/>
+        <f t="shared" si="97"/>
         <v>-0.18648455261557323</v>
       </c>
       <c r="L173" s="346">
-        <f t="shared" si="98"/>
+        <f t="shared" si="97"/>
         <v>-0.2050614572635579</v>
       </c>
     </row>
@@ -13935,19 +13938,19 @@
         <v>-89335094.431522116</v>
       </c>
       <c r="I177" s="236">
-        <f t="shared" ref="I177:L177" si="99">I120+I127</f>
+        <f t="shared" ref="I177:L177" si="98">I120+I127</f>
         <v>-125097258.36987357</v>
       </c>
       <c r="J177" s="236">
-        <f t="shared" si="99"/>
+        <f t="shared" si="98"/>
         <v>-111687933.35635503</v>
       </c>
       <c r="K177" s="236">
-        <f t="shared" si="99"/>
+        <f t="shared" si="98"/>
         <v>-101076069.3912459</v>
       </c>
       <c r="L177" s="236">
-        <f t="shared" si="99"/>
+        <f t="shared" si="98"/>
         <v>-83866228.614133</v>
       </c>
     </row>
@@ -14154,19 +14157,19 @@
         <v>2026</v>
       </c>
       <c r="I188" s="54">
-        <f t="shared" ref="I188" si="100">H188+1</f>
+        <f t="shared" ref="I188" si="99">H188+1</f>
         <v>2027</v>
       </c>
       <c r="J188" s="54">
-        <f t="shared" ref="J188" si="101">I188+1</f>
+        <f t="shared" ref="J188" si="100">I188+1</f>
         <v>2028</v>
       </c>
       <c r="K188" s="54">
-        <f t="shared" ref="K188" si="102">J188+1</f>
+        <f t="shared" ref="K188" si="101">J188+1</f>
         <v>2029</v>
       </c>
       <c r="L188" s="54">
-        <f t="shared" ref="L188" si="103">K188+1</f>
+        <f t="shared" ref="L188" si="102">K188+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -14252,19 +14255,19 @@
         <v>17000000</v>
       </c>
       <c r="I193" s="334">
-        <f t="shared" ref="I193:L193" si="104">H196</f>
+        <f t="shared" ref="I193:L193" si="103">H196</f>
         <v>16500000</v>
       </c>
       <c r="J193" s="334">
-        <f t="shared" si="104"/>
+        <f t="shared" si="103"/>
         <v>16000000</v>
       </c>
       <c r="K193" s="334">
-        <f t="shared" si="104"/>
+        <f t="shared" si="103"/>
         <v>16000000</v>
       </c>
       <c r="L193" s="334">
-        <f t="shared" si="104"/>
+        <f t="shared" si="103"/>
         <v>16250000</v>
       </c>
     </row>
@@ -14349,19 +14352,19 @@
         <v>16500000</v>
       </c>
       <c r="I196" s="338">
-        <f t="shared" ref="I196:L196" si="105">SUM(I193:I195)</f>
+        <f t="shared" ref="I196:L196" si="104">SUM(I193:I195)</f>
         <v>16000000</v>
       </c>
       <c r="J196" s="338">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>16000000</v>
       </c>
       <c r="K196" s="338">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>16250000</v>
       </c>
       <c r="L196" s="338">
-        <f t="shared" si="105"/>
+        <f t="shared" si="104"/>
         <v>16750000</v>
       </c>
     </row>
@@ -14392,7 +14395,7 @@
         <v>3.451776649746193</v>
       </c>
       <c r="G198" s="339">
-        <f t="shared" ref="G198" si="106">G199/G196</f>
+        <f t="shared" ref="G198" si="105">G199/G196</f>
         <v>3.3529411764705883</v>
       </c>
       <c r="H198" s="340">
@@ -14435,19 +14438,19 @@
         <v>55323529.411764704</v>
       </c>
       <c r="I199" s="323">
-        <f t="shared" ref="I199:L199" si="107">I198*I196</f>
+        <f t="shared" ref="I199:L199" si="106">I198*I196</f>
         <v>53647058.823529415</v>
       </c>
       <c r="J199" s="323">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>53647058.823529415</v>
       </c>
       <c r="K199" s="323">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>54485294.117647059</v>
       </c>
       <c r="L199" s="323">
-        <f t="shared" si="107"/>
+        <f t="shared" si="106"/>
         <v>56161764.705882356</v>
       </c>
     </row>
@@ -14518,19 +14521,19 @@
         <v>44.348260000000003</v>
       </c>
       <c r="I202" s="342">
-        <f t="shared" ref="I202:L202" si="108">H202*(1+I201)</f>
+        <f t="shared" ref="I202:L202" si="107">H202*(1+I201)</f>
         <v>45.856100840000003</v>
       </c>
       <c r="J202" s="342">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>47.415208268560008</v>
       </c>
       <c r="K202" s="342">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>49.027325349691047</v>
       </c>
       <c r="L202" s="342">
-        <f t="shared" si="108"/>
+        <f t="shared" si="107"/>
         <v>50.694254411580545</v>
       </c>
     </row>
@@ -14628,19 +14631,19 @@
         <v>2330827153.1470585</v>
       </c>
       <c r="I206" s="229">
-        <f t="shared" ref="I206:L206" si="109">I205*I203</f>
+        <f t="shared" ref="I206:L206" si="108">I205*I203</f>
         <v>2337042692.2221179</v>
       </c>
       <c r="J206" s="229">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>2416502143.7576699</v>
       </c>
       <c r="K206" s="229">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>2537704829.4055157</v>
       </c>
       <c r="L206" s="229">
-        <f t="shared" si="109"/>
+        <f t="shared" si="108"/>
         <v>2704724848.793159</v>
       </c>
     </row>
@@ -14814,23 +14817,23 @@
         <v>138300000</v>
       </c>
       <c r="H214" s="229">
-        <f t="shared" ref="H214:L214" si="110">SUM(H210:H213)</f>
+        <f t="shared" ref="H214:L214" si="109">SUM(H210:H213)</f>
         <v>138300000</v>
       </c>
       <c r="I214" s="229">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>138300000</v>
       </c>
       <c r="J214" s="229">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>138300000</v>
       </c>
       <c r="K214" s="229">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>138300000</v>
       </c>
       <c r="L214" s="229">
-        <f t="shared" si="110"/>
+        <f t="shared" si="109"/>
         <v>138300000</v>
       </c>
     </row>
@@ -14896,19 +14899,19 @@
         <v>2469127153.1470585</v>
       </c>
       <c r="I218" s="212">
-        <f t="shared" ref="I218:L218" si="111">I214+I206</f>
+        <f t="shared" ref="I218:L218" si="110">I214+I206</f>
         <v>2475342692.2221179</v>
       </c>
       <c r="J218" s="212">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>2554802143.7576699</v>
       </c>
       <c r="K218" s="212">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>2676004829.4055157</v>
       </c>
       <c r="L218" s="212">
-        <f t="shared" si="111"/>
+        <f t="shared" si="110"/>
         <v>2843024848.793159</v>
       </c>
     </row>
@@ -15056,19 +15059,19 @@
         <v>2026</v>
       </c>
       <c r="I226" s="54">
-        <f t="shared" ref="I226" si="112">H226+1</f>
+        <f t="shared" ref="I226" si="111">H226+1</f>
         <v>2027</v>
       </c>
       <c r="J226" s="54">
-        <f t="shared" ref="J226" si="113">I226+1</f>
+        <f t="shared" ref="J226" si="112">I226+1</f>
         <v>2028</v>
       </c>
       <c r="K226" s="54">
-        <f t="shared" ref="K226" si="114">J226+1</f>
+        <f t="shared" ref="K226" si="113">J226+1</f>
         <v>2029</v>
       </c>
       <c r="L226" s="54">
-        <f t="shared" ref="L226" si="115">K226+1</f>
+        <f t="shared" ref="L226" si="114">K226+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -15148,31 +15151,31 @@
       <c r="D231" s="185"/>
       <c r="E231" s="204"/>
       <c r="F231" s="329">
-        <f t="shared" ref="F231:L231" si="116">F199</f>
+        <f t="shared" ref="F231:L231" si="115">F199</f>
         <v>68000000</v>
       </c>
       <c r="G231" s="329">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>57000000</v>
       </c>
       <c r="H231" s="329">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>55323529.411764704</v>
       </c>
       <c r="I231" s="329">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>53647058.823529415</v>
       </c>
       <c r="J231" s="329">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>53647058.823529415</v>
       </c>
       <c r="K231" s="329">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>54485294.117647059</v>
       </c>
       <c r="L231" s="329">
-        <f t="shared" si="116"/>
+        <f t="shared" si="115"/>
         <v>56161764.705882356</v>
       </c>
     </row>
@@ -15220,19 +15223,19 @@
         <v>138308823.52941176</v>
       </c>
       <c r="I233" s="323">
-        <f t="shared" ref="I233:L233" si="117">I232*I231</f>
+        <f t="shared" ref="I233:L233" si="116">I232*I231</f>
         <v>134117647.05882354</v>
       </c>
       <c r="J233" s="323">
-        <f t="shared" si="117"/>
+        <f t="shared" si="116"/>
         <v>134117647.05882354</v>
       </c>
       <c r="K233" s="323">
-        <f t="shared" si="117"/>
+        <f t="shared" si="116"/>
         <v>136213235.29411766</v>
       </c>
       <c r="L233" s="323">
-        <f t="shared" si="117"/>
+        <f t="shared" si="116"/>
         <v>140404411.7647059</v>
       </c>
     </row>
@@ -15294,19 +15297,19 @@
         <v>124477941.17647059</v>
       </c>
       <c r="I236" s="323">
-        <f t="shared" ref="I236:L236" si="118">I233*(1-I235)</f>
+        <f t="shared" ref="I236:L236" si="117">I233*(1-I235)</f>
         <v>120705882.35294119</v>
       </c>
       <c r="J236" s="323">
-        <f t="shared" si="118"/>
+        <f t="shared" si="117"/>
         <v>120705882.35294119</v>
       </c>
       <c r="K236" s="323">
-        <f t="shared" si="118"/>
+        <f t="shared" si="117"/>
         <v>122591911.7647059</v>
       </c>
       <c r="L236" s="323">
-        <f t="shared" si="118"/>
+        <f t="shared" si="117"/>
         <v>126363970.5882353</v>
       </c>
     </row>
@@ -15372,19 +15375,19 @@
         <v>10.35</v>
       </c>
       <c r="I239" s="325">
-        <f t="shared" ref="I239:L239" si="119">H239*(1+I238)</f>
+        <f t="shared" ref="I239:L239" si="118">H239*(1+I238)</f>
         <v>10.660500000000001</v>
       </c>
       <c r="J239" s="325">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>10.980315000000001</v>
       </c>
       <c r="K239" s="325">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>11.309724450000001</v>
       </c>
       <c r="L239" s="325">
-        <f t="shared" si="119"/>
+        <f t="shared" si="118"/>
         <v>11.649016183500001</v>
       </c>
     </row>
@@ -15403,19 +15406,19 @@
         <v>1288346691.1764705</v>
       </c>
       <c r="I240" s="327">
-        <f t="shared" ref="I240:L240" si="120">I239*I236</f>
+        <f t="shared" ref="I240:L240" si="119">I239*I236</f>
         <v>1286785058.8235295</v>
       </c>
       <c r="J240" s="327">
-        <f t="shared" si="120"/>
+        <f t="shared" si="119"/>
         <v>1325388610.5882356</v>
       </c>
       <c r="K240" s="327">
-        <f t="shared" si="120"/>
+        <f t="shared" si="119"/>
         <v>1386480741.857537</v>
       </c>
       <c r="L240" s="227">
-        <f t="shared" si="120"/>
+        <f t="shared" si="119"/>
         <v>1472015938.393671</v>
       </c>
     </row>
@@ -15474,19 +15477,19 @@
         <v>-32208667.279411763</v>
       </c>
       <c r="I243" s="236">
-        <f t="shared" ref="I243:L243" si="121">-I242*(I240)</f>
+        <f t="shared" ref="I243:L243" si="120">-I242*(I240)</f>
         <v>-32169626.470588237</v>
       </c>
       <c r="J243" s="236">
-        <f t="shared" si="121"/>
+        <f t="shared" si="120"/>
         <v>-33134715.264705893</v>
       </c>
       <c r="K243" s="236">
-        <f t="shared" si="121"/>
+        <f t="shared" si="120"/>
         <v>-34662018.546438426</v>
       </c>
       <c r="L243" s="236">
-        <f t="shared" si="121"/>
+        <f t="shared" si="120"/>
         <v>-36800398.45984178</v>
       </c>
     </row>
@@ -15594,7 +15597,7 @@
         <v>0.18298969072164947</v>
       </c>
       <c r="G249" s="331">
-        <f t="shared" ref="G249" si="122">ABS(G254/G251)</f>
+        <f t="shared" ref="G249" si="121">ABS(G254/G251)</f>
         <v>0.23294253315394964</v>
       </c>
       <c r="H249" s="328">
@@ -15647,19 +15650,19 @@
         <v>402300000</v>
       </c>
       <c r="I251" s="225">
-        <f t="shared" ref="I251:L251" si="123">H255</f>
+        <f t="shared" ref="I251:L251" si="122">H255</f>
         <v>325616389.75624496</v>
       </c>
       <c r="J251" s="225">
-        <f t="shared" si="123"/>
+        <f t="shared" si="122"/>
         <v>325221703.22320706</v>
       </c>
       <c r="K251" s="225">
-        <f t="shared" si="123"/>
+        <f t="shared" si="122"/>
         <v>334978354.31990337</v>
       </c>
       <c r="L251" s="225">
-        <f t="shared" si="123"/>
+        <f t="shared" si="122"/>
         <v>350418762.8393364</v>
       </c>
     </row>
@@ -15681,19 +15684,19 @@
         <v>1324331748.2121272</v>
       </c>
       <c r="I252" s="236">
-        <f t="shared" ref="I252:L252" si="124">I255-I251-I253-I254</f>
+        <f t="shared" ref="I252:L252" si="123">I255-I251-I253-I254</f>
         <v>1383683276.7123287</v>
       </c>
       <c r="J252" s="236">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1433324317.5942793</v>
       </c>
       <c r="K252" s="236">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1503578839.7873893</v>
       </c>
       <c r="L252" s="236">
-        <f t="shared" si="124"/>
+        <f t="shared" si="123"/>
         <v>1600518231.559622</v>
       </c>
     </row>
@@ -15787,19 +15790,19 @@
         <v>325616389.75624496</v>
       </c>
       <c r="I255" s="229">
-        <f t="shared" ref="I255:L255" si="125">I345</f>
+        <f t="shared" ref="I255:L255" si="124">I345</f>
         <v>325221703.22320706</v>
       </c>
       <c r="J255" s="229">
-        <f t="shared" si="125"/>
+        <f t="shared" si="124"/>
         <v>334978354.31990337</v>
       </c>
       <c r="K255" s="229">
-        <f t="shared" si="125"/>
+        <f t="shared" si="124"/>
         <v>350418762.8393364</v>
       </c>
       <c r="L255" s="229">
-        <f t="shared" si="125"/>
+        <f t="shared" si="124"/>
         <v>372036904.97757846</v>
       </c>
     </row>
@@ -15958,19 +15961,19 @@
         <v>2026</v>
       </c>
       <c r="I265" s="54">
-        <f t="shared" ref="I265" si="126">H265+1</f>
+        <f t="shared" ref="I265" si="125">H265+1</f>
         <v>2027</v>
       </c>
       <c r="J265" s="54">
-        <f t="shared" ref="J265" si="127">I265+1</f>
+        <f t="shared" ref="J265" si="126">I265+1</f>
         <v>2028</v>
       </c>
       <c r="K265" s="54">
-        <f t="shared" ref="K265" si="128">J265+1</f>
+        <f t="shared" ref="K265" si="127">J265+1</f>
         <v>2029</v>
       </c>
       <c r="L265" s="54">
-        <f t="shared" ref="L265" si="129">K265+1</f>
+        <f t="shared" ref="L265" si="128">K265+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -16090,19 +16093,19 @@
         <v>-4.7628157894736836</v>
       </c>
       <c r="I271" s="320">
-        <f t="shared" ref="I271:L271" si="130">H271*(1+I270)</f>
+        <f t="shared" ref="I271:L271" si="129">H271*(1+I270)</f>
         <v>-4.9057002631578941</v>
       </c>
       <c r="J271" s="320">
-        <f t="shared" si="130"/>
+        <f t="shared" si="129"/>
         <v>-5.0528712710526307</v>
       </c>
       <c r="K271" s="320">
-        <f t="shared" si="130"/>
+        <f t="shared" si="129"/>
         <v>-5.2044574091842097</v>
       </c>
       <c r="L271" s="320">
-        <f t="shared" si="130"/>
+        <f t="shared" si="129"/>
         <v>-5.3605911314597359</v>
       </c>
     </row>
@@ -16312,7 +16315,7 @@
         <v>1014700000</v>
       </c>
       <c r="G280" s="212">
-        <f t="shared" ref="G280" si="131">SUM(G276:G279)</f>
+        <f t="shared" ref="G280" si="130">SUM(G276:G279)</f>
         <v>939600000</v>
       </c>
       <c r="H280" s="212"/>
@@ -16350,19 +16353,19 @@
         <v>32655301.722517647</v>
       </c>
       <c r="I282" s="236">
-        <f t="shared" ref="I282:L282" si="132">I442</f>
+        <f t="shared" ref="I282:L282" si="131">I442</f>
         <v>36610877.59881299</v>
       </c>
       <c r="J282" s="236">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>40634993.467596814</v>
       </c>
       <c r="K282" s="236">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>44819639.046127364</v>
       </c>
       <c r="L282" s="236">
-        <f t="shared" si="132"/>
+        <f t="shared" si="131"/>
         <v>49234862.788686305</v>
       </c>
     </row>
@@ -16381,19 +16384,19 @@
         <v>95890948.168181688</v>
       </c>
       <c r="I283" s="236">
-        <f t="shared" ref="I283:L283" si="133">I469</f>
+        <f t="shared" ref="I283:L283" si="132">I469</f>
         <v>112453664.98009716</v>
       </c>
       <c r="J283" s="236">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>129303371.22702277</v>
       </c>
       <c r="K283" s="236">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>146825244.61359733</v>
       </c>
       <c r="L283" s="236">
-        <f t="shared" si="133"/>
+        <f t="shared" si="132"/>
         <v>165312590.77916718</v>
       </c>
     </row>
@@ -16412,19 +16415,19 @@
         <v>17210000</v>
       </c>
       <c r="I284" s="236">
-        <f t="shared" ref="I284:L284" si="134">I395</f>
+        <f t="shared" ref="I284:L284" si="133">I395</f>
         <v>17210000</v>
       </c>
       <c r="J284" s="236">
-        <f t="shared" si="134"/>
+        <f t="shared" si="133"/>
         <v>17210000</v>
       </c>
       <c r="K284" s="236">
-        <f t="shared" si="134"/>
+        <f t="shared" si="133"/>
         <v>17210000</v>
       </c>
       <c r="L284" s="236">
-        <f t="shared" si="134"/>
+        <f t="shared" si="133"/>
         <v>17210000</v>
       </c>
     </row>
@@ -16443,19 +16446,19 @@
         <v>0</v>
       </c>
       <c r="I285" s="193">
-        <f t="shared" ref="I285:L285" si="135">I445</f>
+        <f t="shared" ref="I285:L285" si="134">I445</f>
         <v>0</v>
       </c>
       <c r="J285" s="193">
-        <f t="shared" si="135"/>
+        <f t="shared" si="134"/>
         <v>0</v>
       </c>
       <c r="K285" s="193">
-        <f t="shared" si="135"/>
+        <f t="shared" si="134"/>
         <v>0</v>
       </c>
       <c r="L285" s="193">
-        <f t="shared" si="135"/>
+        <f t="shared" si="134"/>
         <v>0</v>
       </c>
     </row>
@@ -16474,19 +16477,19 @@
         <v>0</v>
       </c>
       <c r="I286" s="193">
-        <f t="shared" ref="I286:L286" si="136">I479</f>
+        <f t="shared" ref="I286:L286" si="135">I479</f>
         <v>0</v>
       </c>
       <c r="J286" s="193">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>0</v>
       </c>
       <c r="K286" s="193">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>0</v>
       </c>
       <c r="L286" s="193">
-        <f t="shared" si="136"/>
+        <f t="shared" si="135"/>
         <v>0</v>
       </c>
     </row>
@@ -16505,19 +16508,19 @@
         <v>0</v>
       </c>
       <c r="I287" s="193">
-        <f t="shared" ref="I287:L287" si="137">-I400</f>
+        <f t="shared" ref="I287:L287" si="136">-I400</f>
         <v>0</v>
       </c>
       <c r="J287" s="193">
-        <f t="shared" si="137"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="K287" s="193">
-        <f t="shared" si="137"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
       <c r="L287" s="193">
-        <f t="shared" si="137"/>
+        <f t="shared" si="136"/>
         <v>0</v>
       </c>
     </row>
@@ -16536,19 +16539,19 @@
         <v>29500000</v>
       </c>
       <c r="I288" s="236">
-        <f t="shared" ref="I288:L288" si="138">-I322</f>
+        <f t="shared" ref="I288:L288" si="137">-I322</f>
         <v>29500000</v>
       </c>
       <c r="J288" s="236">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>29500000</v>
       </c>
       <c r="K288" s="236">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>29500000</v>
       </c>
       <c r="L288" s="236">
-        <f t="shared" si="138"/>
+        <f t="shared" si="137"/>
         <v>29500000</v>
       </c>
     </row>
@@ -16567,19 +16570,19 @@
         <v>53661738.188976377</v>
       </c>
       <c r="I289" s="236">
-        <f t="shared" ref="I289:L289" si="139">-I323</f>
+        <f t="shared" ref="I289:L289" si="138">-I323</f>
         <v>47699322.834645666</v>
       </c>
       <c r="J289" s="236">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>41736907.480314955</v>
       </c>
       <c r="K289" s="236">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>35774492.125984251</v>
       </c>
       <c r="L289" s="236">
-        <f t="shared" si="139"/>
+        <f t="shared" si="138"/>
         <v>29812076.77165354</v>
       </c>
     </row>
@@ -16630,19 +16633,19 @@
         <v>-228917988.0796757</v>
       </c>
       <c r="I291" s="212">
-        <f t="shared" ref="I291:L291" si="140">-SUM(I282:I290)</f>
+        <f t="shared" ref="I291:L291" si="139">-SUM(I282:I290)</f>
         <v>-243473865.4135558</v>
       </c>
       <c r="J291" s="212">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>-258385272.17493457</v>
       </c>
       <c r="K291" s="212">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>-274129375.78570896</v>
       </c>
       <c r="L291" s="212">
-        <f t="shared" si="140"/>
+        <f t="shared" si="139"/>
         <v>-291069530.33950704</v>
       </c>
     </row>
@@ -16738,19 +16741,19 @@
         <v>4.5857581578947366</v>
       </c>
       <c r="I295" s="320">
-        <f t="shared" ref="I295:L295" si="141">H295*(1+I293)*(1-I294)</f>
+        <f t="shared" ref="I295:L295" si="140">H295*(1+I293)*(1-I294)</f>
         <v>4.6760975936052631</v>
       </c>
       <c r="J295" s="320">
-        <f t="shared" si="141"/>
+        <f t="shared" si="140"/>
         <v>4.7682167161992872</v>
       </c>
       <c r="K295" s="320">
-        <f t="shared" si="141"/>
+        <f t="shared" si="140"/>
         <v>4.8621505855084131</v>
       </c>
       <c r="L295" s="320">
-        <f t="shared" si="141"/>
+        <f t="shared" si="140"/>
         <v>4.9579349520429288</v>
       </c>
     </row>
@@ -16940,19 +16943,19 @@
         <v>-785848989.28990126</v>
       </c>
       <c r="I302" s="225">
-        <f t="shared" ref="I302:L302" si="142">(I301+I299+I296)</f>
+        <f t="shared" ref="I302:L302" si="141">(I301+I299+I296)</f>
         <v>-796201230.42997456</v>
       </c>
       <c r="J302" s="225">
-        <f t="shared" si="142"/>
+        <f t="shared" si="141"/>
         <v>-817855515.79650664</v>
       </c>
       <c r="K302" s="225">
-        <f t="shared" si="142"/>
+        <f t="shared" si="141"/>
         <v>-842959229.6928755</v>
       </c>
       <c r="L302" s="225">
-        <f t="shared" si="142"/>
+        <f t="shared" si="141"/>
         <v>-875737141.48277652</v>
       </c>
     </row>
@@ -17016,19 +17019,19 @@
         <v>-1014766977.3695769</v>
       </c>
       <c r="I305" s="229">
-        <f t="shared" ref="I305:L305" si="143">SUM(I302:I304)</f>
+        <f t="shared" ref="I305:L305" si="142">SUM(I302:I304)</f>
         <v>-1039675095.8435304</v>
       </c>
       <c r="J305" s="229">
-        <f t="shared" si="143"/>
+        <f t="shared" si="142"/>
         <v>-1076240787.9714413</v>
       </c>
       <c r="K305" s="229">
-        <f t="shared" si="143"/>
+        <f t="shared" si="142"/>
         <v>-1117088605.4785845</v>
       </c>
       <c r="L305" s="229">
-        <f t="shared" si="143"/>
+        <f t="shared" si="142"/>
         <v>-1166806671.8222835</v>
       </c>
     </row>
@@ -17145,19 +17148,19 @@
         <v>2026</v>
       </c>
       <c r="I312" s="54">
-        <f t="shared" ref="I312" si="144">H312+1</f>
+        <f t="shared" ref="I312" si="143">H312+1</f>
         <v>2027</v>
       </c>
       <c r="J312" s="54">
-        <f t="shared" ref="J312" si="145">I312+1</f>
+        <f t="shared" ref="J312" si="144">I312+1</f>
         <v>2028</v>
       </c>
       <c r="K312" s="54">
-        <f t="shared" ref="K312" si="146">J312+1</f>
+        <f t="shared" ref="K312" si="145">J312+1</f>
         <v>2029</v>
       </c>
       <c r="L312" s="54">
-        <f t="shared" ref="L312" si="147">K312+1</f>
+        <f t="shared" ref="L312" si="146">K312+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -17204,31 +17207,31 @@
       <c r="D315" s="61"/>
       <c r="E315" s="176"/>
       <c r="F315" s="236">
-        <f t="shared" ref="F315:L315" si="148">F61</f>
+        <f t="shared" ref="F315:L315" si="147">F61</f>
         <v>254000000</v>
       </c>
       <c r="G315" s="236">
-        <f t="shared" si="148"/>
+        <f t="shared" si="147"/>
         <v>172100000</v>
       </c>
       <c r="H315" s="236">
-        <f t="shared" si="148"/>
+        <f t="shared" si="147"/>
         <v>154890000</v>
       </c>
       <c r="I315" s="236">
-        <f t="shared" si="148"/>
+        <f t="shared" si="147"/>
         <v>137680000</v>
       </c>
       <c r="J315" s="236">
-        <f t="shared" si="148"/>
+        <f t="shared" si="147"/>
         <v>120470000</v>
       </c>
       <c r="K315" s="236">
-        <f t="shared" si="148"/>
+        <f t="shared" si="147"/>
         <v>103260000</v>
       </c>
       <c r="L315" s="236">
-        <f t="shared" si="148"/>
+        <f t="shared" si="147"/>
         <v>86050000</v>
       </c>
     </row>
@@ -17245,7 +17248,7 @@
         <v>0.27047244094488188</v>
       </c>
       <c r="G316" s="106">
-        <f t="shared" ref="G316" si="149">G317/G315</f>
+        <f t="shared" ref="G316" si="148">G317/G315</f>
         <v>0.42242882045322488</v>
       </c>
       <c r="H316" s="295">
@@ -17257,11 +17260,11 @@
         <v>0.34645063069905335</v>
       </c>
       <c r="J316" s="295">
-        <f t="shared" ref="J316:K316" si="150">I316</f>
+        <f t="shared" ref="J316:K316" si="149">I316</f>
         <v>0.34645063069905335</v>
       </c>
       <c r="K316" s="295">
-        <f t="shared" si="150"/>
+        <f t="shared" si="149"/>
         <v>0.34645063069905335</v>
       </c>
       <c r="L316" s="295">
@@ -17288,19 +17291,19 @@
         <v>53661738.188976377</v>
       </c>
       <c r="I317" s="229">
-        <f t="shared" ref="I317:L317" si="151">I316*I315</f>
+        <f t="shared" ref="I317:L317" si="150">I316*I315</f>
         <v>47699322.834645666</v>
       </c>
       <c r="J317" s="229">
-        <f t="shared" si="151"/>
+        <f t="shared" si="150"/>
         <v>41736907.480314955</v>
       </c>
       <c r="K317" s="229">
-        <f t="shared" si="151"/>
+        <f t="shared" si="150"/>
         <v>35774492.125984251</v>
       </c>
       <c r="L317" s="229">
-        <f t="shared" si="151"/>
+        <f t="shared" si="150"/>
         <v>29812076.77165354</v>
       </c>
     </row>
@@ -17392,23 +17395,23 @@
         <v>-29500000</v>
       </c>
       <c r="H322" s="236">
-        <f t="shared" ref="H322:L322" si="152">-H319</f>
+        <f t="shared" ref="H322:L322" si="151">-H319</f>
         <v>-29500000</v>
       </c>
       <c r="I322" s="236">
-        <f t="shared" si="152"/>
+        <f t="shared" si="151"/>
         <v>-29500000</v>
       </c>
       <c r="J322" s="236">
-        <f t="shared" si="152"/>
+        <f t="shared" si="151"/>
         <v>-29500000</v>
       </c>
       <c r="K322" s="236">
-        <f t="shared" si="152"/>
+        <f t="shared" si="151"/>
         <v>-29500000</v>
       </c>
       <c r="L322" s="236">
-        <f t="shared" si="152"/>
+        <f t="shared" si="151"/>
         <v>-29500000</v>
       </c>
     </row>
@@ -17433,19 +17436,19 @@
         <v>-53661738.188976377</v>
       </c>
       <c r="I323" s="236">
-        <f t="shared" ref="I323:L323" si="153">-I317</f>
+        <f t="shared" ref="I323:L323" si="152">-I317</f>
         <v>-47699322.834645666</v>
       </c>
       <c r="J323" s="236">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>-41736907.480314955</v>
       </c>
       <c r="K323" s="236">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>-35774492.125984251</v>
       </c>
       <c r="L323" s="236">
-        <f t="shared" si="153"/>
+        <f t="shared" si="152"/>
         <v>-29812076.77165354</v>
       </c>
     </row>
@@ -17470,19 +17473,19 @@
         <v>-83161738.188976377</v>
       </c>
       <c r="I324" s="225">
-        <f t="shared" ref="I324" si="154">SUM(I322:I323)</f>
+        <f t="shared" ref="I324" si="153">SUM(I322:I323)</f>
         <v>-77199322.834645659</v>
       </c>
       <c r="J324" s="225">
-        <f t="shared" ref="J324" si="155">SUM(J322:J323)</f>
+        <f t="shared" ref="J324" si="154">SUM(J322:J323)</f>
         <v>-71236907.480314955</v>
       </c>
       <c r="K324" s="225">
-        <f t="shared" ref="K324" si="156">SUM(K322:K323)</f>
+        <f t="shared" ref="K324" si="155">SUM(K322:K323)</f>
         <v>-65274492.125984251</v>
       </c>
       <c r="L324" s="225">
-        <f t="shared" ref="L324" si="157">SUM(L322:L323)</f>
+        <f t="shared" ref="L324" si="156">SUM(L322:L323)</f>
         <v>-59312076.77165354</v>
       </c>
     </row>
@@ -17501,19 +17504,19 @@
         <v>19038261.811023623</v>
       </c>
       <c r="I325" s="262">
-        <f t="shared" ref="I325:L325" si="158">I324-H324</f>
+        <f t="shared" ref="I325:L325" si="157">I324-H324</f>
         <v>5962415.3543307185</v>
       </c>
       <c r="J325" s="262">
-        <f t="shared" si="158"/>
+        <f t="shared" si="157"/>
         <v>5962415.3543307036</v>
       </c>
       <c r="K325" s="262">
-        <f t="shared" si="158"/>
+        <f t="shared" si="157"/>
         <v>5962415.3543307036</v>
       </c>
       <c r="L325" s="262">
-        <f t="shared" si="158"/>
+        <f t="shared" si="157"/>
         <v>5962415.3543307111</v>
       </c>
     </row>
@@ -17549,19 +17552,19 @@
         <v>4.3052837573385516E-2</v>
       </c>
       <c r="I327" s="295">
-        <f t="shared" ref="I327:L327" si="159">H327</f>
+        <f t="shared" ref="I327:L327" si="158">H327</f>
         <v>4.3052837573385516E-2</v>
       </c>
       <c r="J327" s="295">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>4.3052837573385516E-2</v>
       </c>
       <c r="K327" s="295">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>4.3052837573385516E-2</v>
       </c>
       <c r="L327" s="295">
-        <f t="shared" si="159"/>
+        <f t="shared" si="158"/>
         <v>4.3052837573385516E-2</v>
       </c>
     </row>
@@ -17579,23 +17582,23 @@
         <v>0.95694716242661448</v>
       </c>
       <c r="H328" s="295">
-        <f t="shared" ref="H328:L328" si="160">G328</f>
+        <f t="shared" ref="H328:L328" si="159">G328</f>
         <v>0.95694716242661448</v>
       </c>
       <c r="I328" s="295">
-        <f t="shared" si="160"/>
+        <f t="shared" si="159"/>
         <v>0.95694716242661448</v>
       </c>
       <c r="J328" s="295">
-        <f t="shared" si="160"/>
+        <f t="shared" si="159"/>
         <v>0.95694716242661448</v>
       </c>
       <c r="K328" s="295">
-        <f t="shared" si="160"/>
+        <f t="shared" si="159"/>
         <v>0.95694716242661448</v>
       </c>
       <c r="L328" s="295">
-        <f t="shared" si="160"/>
+        <f t="shared" si="159"/>
         <v>0.95694716242661448</v>
       </c>
     </row>
@@ -17774,19 +17777,19 @@
         <v>2026</v>
       </c>
       <c r="I337" s="54">
-        <f t="shared" ref="I337" si="161">H337+1</f>
+        <f t="shared" ref="I337" si="160">H337+1</f>
         <v>2027</v>
       </c>
       <c r="J337" s="54">
-        <f t="shared" ref="J337" si="162">I337+1</f>
+        <f t="shared" ref="J337" si="161">I337+1</f>
         <v>2028</v>
       </c>
       <c r="K337" s="54">
-        <f t="shared" ref="K337" si="163">J337+1</f>
+        <f t="shared" ref="K337" si="162">J337+1</f>
         <v>2029</v>
       </c>
       <c r="L337" s="54">
-        <f t="shared" ref="L337" si="164">K337+1</f>
+        <f t="shared" ref="L337" si="163">K337+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -17907,19 +17910,19 @@
         <v>49382543.062941171</v>
       </c>
       <c r="I344" s="236">
-        <f t="shared" ref="I344:L344" si="165">I360*I357</f>
+        <f t="shared" ref="I344:L344" si="164">I360*I357</f>
         <v>49506853.84444236</v>
       </c>
       <c r="J344" s="236">
-        <f t="shared" si="165"/>
+        <f t="shared" si="164"/>
         <v>51096042.8751534</v>
       </c>
       <c r="K344" s="236">
-        <f t="shared" si="165"/>
+        <f t="shared" si="164"/>
         <v>53520096.588110313</v>
       </c>
       <c r="L344" s="236">
-        <f t="shared" si="165"/>
+        <f t="shared" si="164"/>
         <v>56860496.975863181</v>
       </c>
     </row>
@@ -17973,27 +17976,27 @@
         <v>573700000</v>
       </c>
       <c r="G346" s="246">
-        <f t="shared" ref="G346:L346" si="166">SUM(G344:G345)</f>
+        <f t="shared" ref="G346:L346" si="165">SUM(G344:G345)</f>
         <v>451500000</v>
       </c>
       <c r="H346" s="246">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>374998932.81918615</v>
       </c>
       <c r="I346" s="246">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>374728557.06764942</v>
       </c>
       <c r="J346" s="246">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>386074397.1950568</v>
       </c>
       <c r="K346" s="246">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>403938859.42744672</v>
       </c>
       <c r="L346" s="246">
-        <f t="shared" si="166"/>
+        <f t="shared" si="165"/>
         <v>428897401.95344162</v>
       </c>
     </row>
@@ -18032,19 +18035,19 @@
         <v>594249911.30514705</v>
       </c>
       <c r="I348" s="236">
-        <f t="shared" ref="I348:L348" si="167">I362*ABS(I358)</f>
+        <f t="shared" ref="I348:L348" si="166">I362*ABS(I358)</f>
         <v>593529608.38235295</v>
       </c>
       <c r="J348" s="236">
-        <f t="shared" si="167"/>
+        <f t="shared" si="166"/>
         <v>611335496.63382375</v>
       </c>
       <c r="K348" s="236">
-        <f t="shared" si="167"/>
+        <f t="shared" si="166"/>
         <v>639514242.18178904</v>
       </c>
       <c r="L348" s="236">
-        <f t="shared" si="167"/>
+        <f t="shared" si="166"/>
         <v>678967351.58408082</v>
       </c>
     </row>
@@ -18057,31 +18060,31 @@
       <c r="D349" s="185"/>
       <c r="E349" s="204"/>
       <c r="F349" s="246">
-        <f t="shared" ref="F349:L349" si="168">SUM(F348:F348)</f>
+        <f t="shared" ref="F349:L349" si="167">SUM(F348:F348)</f>
         <v>671700000</v>
       </c>
       <c r="G349" s="246">
-        <f t="shared" si="168"/>
+        <f t="shared" si="167"/>
         <v>619300000</v>
       </c>
       <c r="H349" s="246">
-        <f t="shared" si="168"/>
+        <f t="shared" si="167"/>
         <v>594249911.30514705</v>
       </c>
       <c r="I349" s="246">
-        <f t="shared" si="168"/>
+        <f t="shared" si="167"/>
         <v>593529608.38235295</v>
       </c>
       <c r="J349" s="246">
-        <f t="shared" si="168"/>
+        <f t="shared" si="167"/>
         <v>611335496.63382375</v>
       </c>
       <c r="K349" s="246">
-        <f t="shared" si="168"/>
+        <f t="shared" si="167"/>
         <v>639514242.18178904</v>
       </c>
       <c r="L349" s="246">
-        <f t="shared" si="168"/>
+        <f t="shared" si="167"/>
         <v>678967351.58408082</v>
       </c>
     </row>
@@ -18108,31 +18111,31 @@
       <c r="D351" s="185"/>
       <c r="E351" s="204"/>
       <c r="F351" s="225">
-        <f t="shared" ref="F351:L351" si="169">F346-F349</f>
+        <f t="shared" ref="F351:L351" si="168">F346-F349</f>
         <v>-98000000</v>
       </c>
       <c r="G351" s="225">
-        <f t="shared" si="169"/>
+        <f t="shared" si="168"/>
         <v>-167800000</v>
       </c>
       <c r="H351" s="225">
-        <f t="shared" si="169"/>
+        <f t="shared" si="168"/>
         <v>-219250978.4859609</v>
       </c>
       <c r="I351" s="225">
-        <f t="shared" si="169"/>
+        <f t="shared" si="168"/>
         <v>-218801051.31470352</v>
       </c>
       <c r="J351" s="225">
-        <f t="shared" si="169"/>
+        <f t="shared" si="168"/>
         <v>-225261099.43876696</v>
       </c>
       <c r="K351" s="225">
-        <f t="shared" si="169"/>
+        <f t="shared" si="168"/>
         <v>-235575382.75434232</v>
       </c>
       <c r="L351" s="225">
-        <f t="shared" si="169"/>
+        <f t="shared" si="168"/>
         <v>-250069949.6306392</v>
       </c>
     </row>
@@ -18151,19 +18154,19 @@
         <v>-51450978.485960901</v>
       </c>
       <c r="I352" s="225">
-        <f t="shared" ref="I352:L352" si="170">I351-H351</f>
+        <f t="shared" ref="I352:L352" si="169">I351-H351</f>
         <v>449927.17125737667</v>
       </c>
       <c r="J352" s="225">
-        <f t="shared" si="170"/>
+        <f t="shared" si="169"/>
         <v>-6460048.1240634322</v>
       </c>
       <c r="K352" s="225">
-        <f t="shared" si="170"/>
+        <f t="shared" si="169"/>
         <v>-10314283.315575361</v>
       </c>
       <c r="L352" s="225">
-        <f t="shared" si="170"/>
+        <f t="shared" si="169"/>
         <v>-14494566.876296878</v>
       </c>
     </row>
@@ -18234,31 +18237,31 @@
       <c r="D357" s="61"/>
       <c r="E357" s="61"/>
       <c r="F357" s="236">
-        <f t="shared" ref="F357:L358" si="171">F10</f>
+        <f t="shared" ref="F357:L358" si="170">F10</f>
         <v>2905800000</v>
       </c>
       <c r="G357" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>2477800000</v>
       </c>
       <c r="H357" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>2469127153.1470585</v>
       </c>
       <c r="I357" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>2475342692.2221179</v>
       </c>
       <c r="J357" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>2554802143.7576699</v>
       </c>
       <c r="K357" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>2676004829.4055157</v>
       </c>
       <c r="L357" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>2843024848.793159</v>
       </c>
     </row>
@@ -18271,31 +18274,31 @@
       <c r="D358" s="61"/>
       <c r="E358" s="61"/>
       <c r="F358" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>-1743300000</v>
       </c>
       <c r="G358" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>-1311100000</v>
       </c>
       <c r="H358" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>-1320555358.4558823</v>
       </c>
       <c r="I358" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>-1318954685.2941177</v>
       </c>
       <c r="J358" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>-1358523325.8529415</v>
       </c>
       <c r="K358" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>-1421142760.4039755</v>
       </c>
       <c r="L358" s="236">
-        <f t="shared" si="171"/>
+        <f t="shared" si="170"/>
         <v>-1508816336.8535128</v>
       </c>
     </row>
@@ -18354,31 +18357,31 @@
       <c r="D361" s="61"/>
       <c r="E361" s="61"/>
       <c r="F361" s="366">
-        <f t="shared" ref="F361:L361" si="172">F345/ABS(F358)</f>
+        <f t="shared" ref="F361:L361" si="171">F345/ABS(F358)</f>
         <v>0.29845694946366086</v>
       </c>
       <c r="G361" s="366">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.30684158340324919</v>
       </c>
       <c r="H361" s="367">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.24657534246575344</v>
       </c>
       <c r="I361" s="367">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.24657534246575338</v>
       </c>
       <c r="J361" s="367">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.24657534246575341</v>
       </c>
       <c r="K361" s="367">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.24657534246575341</v>
       </c>
       <c r="L361" s="367">
-        <f t="shared" si="172"/>
+        <f t="shared" si="171"/>
         <v>0.24657534246575341</v>
       </c>
     </row>
@@ -18470,31 +18473,31 @@
       <c r="D366" s="44"/>
       <c r="E366" s="44"/>
       <c r="F366" s="368">
-        <f t="shared" ref="F366:L366" si="173">F344/F357*$D$340</f>
+        <f t="shared" ref="F366:L366" si="172">F344/F357*$D$340</f>
         <v>6.7076192442700808</v>
       </c>
       <c r="G366" s="368">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>7.2475583178626204</v>
       </c>
       <c r="H366" s="368">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>7.3</v>
       </c>
       <c r="I366" s="368">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>7.3</v>
       </c>
       <c r="J366" s="368">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>7.3</v>
       </c>
       <c r="K366" s="368">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>7.3</v>
       </c>
       <c r="L366" s="368">
-        <f t="shared" si="173"/>
+        <f t="shared" si="172"/>
         <v>7.3</v>
       </c>
     </row>
@@ -18539,31 +18542,31 @@
       <c r="D368" s="44"/>
       <c r="E368" s="44"/>
       <c r="F368" s="368">
-        <f t="shared" ref="F368:L368" si="174">ABS(F348/F358)*$D$340</f>
+        <f t="shared" ref="F368:L368" si="173">ABS(F348/F358)*$D$340</f>
         <v>140.63586301841337</v>
       </c>
       <c r="G368" s="368">
-        <f t="shared" si="174"/>
+        <f t="shared" si="173"/>
         <v>172.40828312104341</v>
       </c>
       <c r="H368" s="368">
-        <f t="shared" si="174"/>
+        <f t="shared" si="173"/>
         <v>164.25</v>
       </c>
       <c r="I368" s="368">
-        <f t="shared" si="174"/>
+        <f t="shared" si="173"/>
         <v>164.25</v>
       </c>
       <c r="J368" s="368">
-        <f t="shared" si="174"/>
+        <f t="shared" si="173"/>
         <v>164.25000000000003</v>
       </c>
       <c r="K368" s="368">
-        <f t="shared" si="174"/>
+        <f t="shared" si="173"/>
         <v>164.25000000000003</v>
       </c>
       <c r="L368" s="368">
-        <f t="shared" si="174"/>
+        <f t="shared" si="173"/>
         <v>164.25000000000003</v>
       </c>
     </row>
@@ -18594,27 +18597,27 @@
         <v>-24.99145721990709</v>
       </c>
       <c r="G370" s="368">
-        <f t="shared" ref="G370:L370" si="175">G367+G366-G368</f>
+        <f t="shared" ref="G370:L370" si="174">G367+G366-G368</f>
         <v>-53.163546860994828</v>
       </c>
       <c r="H370" s="368">
-        <f t="shared" si="175"/>
+        <f t="shared" si="174"/>
         <v>-66.95</v>
       </c>
       <c r="I370" s="368">
-        <f t="shared" si="175"/>
+        <f t="shared" si="174"/>
         <v>-66.95</v>
       </c>
       <c r="J370" s="368">
-        <f t="shared" si="175"/>
+        <f t="shared" si="174"/>
         <v>-66.950000000000031</v>
       </c>
       <c r="K370" s="368">
-        <f t="shared" si="175"/>
+        <f t="shared" si="174"/>
         <v>-66.950000000000031</v>
       </c>
       <c r="L370" s="368">
-        <f t="shared" si="175"/>
+        <f t="shared" si="174"/>
         <v>-66.950000000000031</v>
       </c>
     </row>
@@ -18731,19 +18734,19 @@
         <v>2026</v>
       </c>
       <c r="I377" s="54">
-        <f t="shared" ref="I377" si="176">H377+1</f>
+        <f t="shared" ref="I377" si="175">H377+1</f>
         <v>2027</v>
       </c>
       <c r="J377" s="54">
-        <f t="shared" ref="J377" si="177">I377+1</f>
+        <f t="shared" ref="J377" si="176">I377+1</f>
         <v>2028</v>
       </c>
       <c r="K377" s="54">
-        <f t="shared" ref="K377" si="178">J377+1</f>
+        <f t="shared" ref="K377" si="177">J377+1</f>
         <v>2029</v>
       </c>
       <c r="L377" s="54">
-        <f t="shared" ref="L377" si="179">K377+1</f>
+        <f t="shared" ref="L377" si="178">K377+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -19071,19 +19074,19 @@
         <v>0</v>
       </c>
       <c r="I393" s="236">
-        <f t="shared" ref="I393:L393" si="180">SUM(I387:I391)</f>
+        <f t="shared" ref="I393:L393" si="179">SUM(I387:I391)</f>
         <v>0</v>
       </c>
       <c r="J393" s="236">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="K393" s="236">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
       <c r="L393" s="236">
-        <f t="shared" si="180"/>
+        <f t="shared" si="179"/>
         <v>0</v>
       </c>
     </row>
@@ -19133,19 +19136,19 @@
         <v>17210000</v>
       </c>
       <c r="I395" s="246">
-        <f t="shared" ref="I395:L395" si="181">SUM(I393:I394)</f>
+        <f t="shared" ref="I395:L395" si="180">SUM(I393:I394)</f>
         <v>17210000</v>
       </c>
       <c r="J395" s="246">
-        <f t="shared" si="181"/>
+        <f t="shared" si="180"/>
         <v>17210000</v>
       </c>
       <c r="K395" s="246">
-        <f t="shared" si="181"/>
+        <f t="shared" si="180"/>
         <v>17210000</v>
       </c>
       <c r="L395" s="246">
-        <f t="shared" si="181"/>
+        <f t="shared" si="180"/>
         <v>17210000</v>
       </c>
     </row>
@@ -19182,15 +19185,15 @@
         <v>154890000</v>
       </c>
       <c r="J397" s="225">
-        <f t="shared" ref="J397:L397" si="182">I401</f>
+        <f t="shared" ref="J397:L397" si="181">I401</f>
         <v>137680000</v>
       </c>
       <c r="K397" s="225">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>120470000</v>
       </c>
       <c r="L397" s="225">
-        <f t="shared" si="182"/>
+        <f t="shared" si="181"/>
         <v>103260000</v>
       </c>
     </row>
@@ -19372,19 +19375,19 @@
         <v>-224500000</v>
       </c>
       <c r="I405" s="236">
-        <f t="shared" ref="I405:L405" si="183">I409</f>
+        <f t="shared" ref="I405:L405" si="182">I409</f>
         <v>-199135000</v>
       </c>
       <c r="J405" s="236">
-        <f t="shared" si="183"/>
+        <f t="shared" si="182"/>
         <v>-173009050</v>
       </c>
       <c r="K405" s="236">
-        <f t="shared" si="183"/>
+        <f t="shared" si="182"/>
         <v>-146099321.5</v>
       </c>
       <c r="L405" s="236">
-        <f t="shared" si="183"/>
+        <f t="shared" si="182"/>
         <v>-118382301.14500001</v>
       </c>
     </row>
@@ -19435,19 +19438,19 @@
         <v>-6735000</v>
       </c>
       <c r="I407" s="229">
-        <f t="shared" ref="I407:L407" si="184">I405*I406</f>
+        <f t="shared" ref="I407:L407" si="183">I405*I406</f>
         <v>-5974050</v>
       </c>
       <c r="J407" s="229">
-        <f t="shared" si="184"/>
+        <f t="shared" si="183"/>
         <v>-5190271.5</v>
       </c>
       <c r="K407" s="229">
-        <f t="shared" si="184"/>
+        <f t="shared" si="183"/>
         <v>-4382979.6449999996</v>
       </c>
       <c r="L407" s="229">
-        <f t="shared" si="184"/>
+        <f t="shared" si="183"/>
         <v>-3551469.0343500003</v>
       </c>
     </row>
@@ -19484,15 +19487,15 @@
         <v>-199135000</v>
       </c>
       <c r="J409" s="236">
-        <f t="shared" ref="J409:L409" si="185">I413</f>
+        <f t="shared" ref="J409:L409" si="184">I413</f>
         <v>-173009050</v>
       </c>
       <c r="K409" s="236">
-        <f t="shared" si="185"/>
+        <f t="shared" si="184"/>
         <v>-146099321.5</v>
       </c>
       <c r="L409" s="236">
-        <f t="shared" si="185"/>
+        <f t="shared" si="184"/>
         <v>-118382301.14500001</v>
       </c>
     </row>
@@ -19550,19 +19553,19 @@
         <v>-6735000</v>
       </c>
       <c r="I411" s="236">
-        <f t="shared" ref="I411:L411" si="186">I407</f>
+        <f t="shared" ref="I411:L411" si="185">I407</f>
         <v>-5974050</v>
       </c>
       <c r="J411" s="236">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>-5190271.5</v>
       </c>
       <c r="K411" s="236">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>-4382979.6449999996</v>
       </c>
       <c r="L411" s="236">
-        <f t="shared" si="186"/>
+        <f t="shared" si="185"/>
         <v>-3551469.0343500003</v>
       </c>
     </row>
@@ -19615,15 +19618,15 @@
         <v>-173009050</v>
       </c>
       <c r="J413" s="229">
-        <f t="shared" ref="J413:L413" si="187">SUM(J409:J412)</f>
+        <f t="shared" ref="J413:L413" si="186">SUM(J409:J412)</f>
         <v>-146099321.5</v>
       </c>
       <c r="K413" s="229">
-        <f t="shared" si="187"/>
+        <f t="shared" si="186"/>
         <v>-118382301.14500001</v>
       </c>
       <c r="L413" s="229">
-        <f t="shared" si="187"/>
+        <f t="shared" si="186"/>
         <v>-89833770.179350019</v>
       </c>
     </row>
@@ -19660,15 +19663,15 @@
         <v>26125950</v>
       </c>
       <c r="J415" s="236">
-        <f t="shared" ref="J415:L415" si="188">J412+J411</f>
+        <f t="shared" ref="J415:L415" si="187">J412+J411</f>
         <v>26909728.5</v>
       </c>
       <c r="K415" s="236">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>27717020.355</v>
       </c>
       <c r="L415" s="236">
-        <f t="shared" si="188"/>
+        <f t="shared" si="187"/>
         <v>28548530.96565</v>
       </c>
     </row>
@@ -19687,19 +19690,19 @@
         <v>-26125950</v>
       </c>
       <c r="I416" s="236">
-        <f t="shared" ref="I416:L416" si="189">-(J412+J411)</f>
+        <f t="shared" ref="I416:L416" si="188">-(J412+J411)</f>
         <v>-26909728.5</v>
       </c>
       <c r="J416" s="236">
-        <f t="shared" si="189"/>
+        <f t="shared" si="188"/>
         <v>-27717020.355</v>
       </c>
       <c r="K416" s="236">
-        <f t="shared" si="189"/>
+        <f t="shared" si="188"/>
         <v>-28548530.96565</v>
       </c>
       <c r="L416" s="236">
-        <f t="shared" si="189"/>
+        <f t="shared" si="188"/>
         <v>0</v>
       </c>
     </row>
@@ -19833,19 +19836,19 @@
         <v>2026</v>
       </c>
       <c r="I423" s="54">
-        <f t="shared" ref="I423" si="190">H423+1</f>
+        <f t="shared" ref="I423" si="189">H423+1</f>
         <v>2027</v>
       </c>
       <c r="J423" s="54">
-        <f t="shared" ref="J423" si="191">I423+1</f>
+        <f t="shared" ref="J423" si="190">I423+1</f>
         <v>2028</v>
       </c>
       <c r="K423" s="54">
-        <f t="shared" ref="K423" si="192">J423+1</f>
+        <f t="shared" ref="K423" si="191">J423+1</f>
         <v>2029</v>
       </c>
       <c r="L423" s="54">
-        <f t="shared" ref="L423" si="193">K423+1</f>
+        <f t="shared" ref="L423" si="192">K423+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -20205,19 +20208,19 @@
       <c r="F440" s="96"/>
       <c r="G440" s="96"/>
       <c r="H440" s="236">
-        <f t="shared" ref="H440:K440" si="194">SUM(H434:H438)</f>
+        <f t="shared" ref="H440:K440" si="193">SUM(H434:H438)</f>
         <v>1975301.7225176468</v>
       </c>
       <c r="I440" s="236">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>5930877.598812988</v>
       </c>
       <c r="J440" s="236">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>9954993.4675968178</v>
       </c>
       <c r="K440" s="236">
-        <f t="shared" si="194"/>
+        <f t="shared" si="193"/>
         <v>14139639.046127368</v>
       </c>
       <c r="L440" s="236">
@@ -20271,19 +20274,19 @@
         <v>32655301.722517647</v>
       </c>
       <c r="I442" s="246">
-        <f t="shared" ref="I442:L442" si="195">SUM(I440:I441)</f>
+        <f t="shared" ref="I442:L442" si="194">SUM(I440:I441)</f>
         <v>36610877.59881299</v>
       </c>
       <c r="J442" s="246">
-        <f t="shared" si="195"/>
+        <f t="shared" si="194"/>
         <v>40634993.467596814</v>
       </c>
       <c r="K442" s="246">
-        <f t="shared" si="195"/>
+        <f t="shared" si="194"/>
         <v>44819639.046127364</v>
       </c>
       <c r="L442" s="246">
-        <f t="shared" si="195"/>
+        <f t="shared" si="194"/>
         <v>49234862.788686305</v>
       </c>
     </row>
@@ -20342,19 +20345,19 @@
         <v>0</v>
       </c>
       <c r="I445" s="246">
-        <f t="shared" ref="I445:L445" si="196">SUM(I444)</f>
+        <f t="shared" ref="I445:L445" si="195">SUM(I444)</f>
         <v>0</v>
       </c>
       <c r="J445" s="246">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="K445" s="246">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
       <c r="L445" s="246">
-        <f t="shared" si="196"/>
+        <f t="shared" si="195"/>
         <v>0</v>
       </c>
     </row>
@@ -20391,15 +20394,15 @@
         <v>140497715.50265881</v>
       </c>
       <c r="J447" s="236">
-        <f t="shared" ref="J447:L447" si="197">I451</f>
+        <f t="shared" ref="J447:L447" si="196">I451</f>
         <v>123689579.44162276</v>
       </c>
       <c r="K447" s="236">
-        <f t="shared" si="197"/>
+        <f t="shared" si="196"/>
         <v>103493003.12408732</v>
       </c>
       <c r="L447" s="236">
-        <f t="shared" si="197"/>
+        <f t="shared" si="196"/>
         <v>80081402.713204086</v>
       </c>
     </row>
@@ -20480,19 +20483,19 @@
         <v>0</v>
       </c>
       <c r="I450" s="236">
-        <f t="shared" ref="I450:L450" si="198">-I445</f>
+        <f t="shared" ref="I450:L450" si="197">-I445</f>
         <v>0</v>
       </c>
       <c r="J450" s="236">
-        <f t="shared" si="198"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="K450" s="236">
-        <f t="shared" si="198"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
       <c r="L450" s="236">
-        <f t="shared" si="198"/>
+        <f t="shared" si="197"/>
         <v>0</v>
       </c>
     </row>
@@ -20511,19 +20514,19 @@
         <v>140497715.50265881</v>
       </c>
       <c r="I451" s="246">
-        <f t="shared" ref="I451:L451" si="199">SUM(I447:I450)</f>
+        <f t="shared" ref="I451:L451" si="198">SUM(I447:I450)</f>
         <v>123689579.44162276</v>
       </c>
       <c r="J451" s="246">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>103493003.12408732</v>
       </c>
       <c r="K451" s="246">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>80081402.713204086</v>
       </c>
       <c r="L451" s="246">
-        <f t="shared" si="199"/>
+        <f t="shared" si="198"/>
         <v>53590738.714863062</v>
       </c>
     </row>
@@ -20864,19 +20867,19 @@
       <c r="F467" s="96"/>
       <c r="G467" s="96"/>
       <c r="H467" s="236">
-        <f t="shared" ref="H467:K467" si="200">SUM(H461:H465)</f>
+        <f t="shared" ref="H467:K467" si="199">SUM(H461:H465)</f>
         <v>8270948.1681816876</v>
       </c>
       <c r="I467" s="236">
-        <f t="shared" si="200"/>
+        <f t="shared" si="199"/>
         <v>24833664.980097163</v>
       </c>
       <c r="J467" s="236">
-        <f t="shared" si="200"/>
+        <f t="shared" si="199"/>
         <v>41683371.22702276</v>
       </c>
       <c r="K467" s="236">
-        <f t="shared" si="200"/>
+        <f t="shared" si="199"/>
         <v>59205244.613597319</v>
       </c>
       <c r="L467" s="236">
@@ -20930,19 +20933,19 @@
         <v>95890948.168181688</v>
       </c>
       <c r="I469" s="246">
-        <f t="shared" ref="I469:L469" si="201">SUM(I467:I468)</f>
+        <f t="shared" ref="I469:L469" si="200">SUM(I467:I468)</f>
         <v>112453664.98009716</v>
       </c>
       <c r="J469" s="246">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>129303371.22702277</v>
       </c>
       <c r="K469" s="246">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>146825244.61359733</v>
       </c>
       <c r="L469" s="246">
-        <f t="shared" si="201"/>
+        <f t="shared" si="200"/>
         <v>165312590.77916718</v>
       </c>
     </row>
@@ -20979,15 +20982,15 @@
         <v>460418533.51363516</v>
       </c>
       <c r="J471" s="236">
-        <f t="shared" ref="J471:L471" si="202">I481</f>
+        <f t="shared" ref="J471:L471" si="201">I481</f>
         <v>430882554.97087586</v>
       </c>
       <c r="K471" s="236">
-        <f t="shared" si="202"/>
+        <f t="shared" si="201"/>
         <v>387158559.77577114</v>
       </c>
       <c r="L471" s="236">
-        <f t="shared" si="202"/>
+        <f t="shared" si="201"/>
         <v>329972672.9960013</v>
       </c>
     </row>
@@ -21009,15 +21012,15 @@
         <v>35500000</v>
       </c>
       <c r="J472" s="236">
-        <f t="shared" ref="J472:L472" si="203">I472</f>
+        <f t="shared" ref="J472:L472" si="202">I472</f>
         <v>35500000</v>
       </c>
       <c r="K472" s="236">
-        <f t="shared" si="203"/>
+        <f t="shared" si="202"/>
         <v>35500000</v>
       </c>
       <c r="L472" s="236">
-        <f t="shared" si="203"/>
+        <f t="shared" si="202"/>
         <v>35500000</v>
       </c>
     </row>
@@ -21036,19 +21039,19 @@
         <v>438100000</v>
       </c>
       <c r="I473" s="229">
-        <f t="shared" ref="I473:L473" si="204">I471-I472</f>
+        <f t="shared" ref="I473:L473" si="203">I471-I472</f>
         <v>424918533.51363516</v>
       </c>
       <c r="J473" s="229">
-        <f t="shared" si="204"/>
+        <f t="shared" si="203"/>
         <v>395382554.97087586</v>
       </c>
       <c r="K473" s="229">
-        <f t="shared" si="204"/>
+        <f t="shared" si="203"/>
         <v>351658559.77577114</v>
       </c>
       <c r="L473" s="229">
-        <f t="shared" si="204"/>
+        <f t="shared" si="203"/>
         <v>294472672.9960013</v>
       </c>
     </row>
@@ -21081,19 +21084,19 @@
         <v>82709481.681816876</v>
       </c>
       <c r="I475" s="236">
-        <f t="shared" ref="I475:L475" si="205">I455</f>
+        <f t="shared" ref="I475:L475" si="204">I455</f>
         <v>82917686.437337875</v>
       </c>
       <c r="J475" s="236">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>85579376.031918079</v>
       </c>
       <c r="K475" s="236">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>89639357.83382751</v>
       </c>
       <c r="L475" s="236">
-        <f t="shared" si="205"/>
+        <f t="shared" si="204"/>
         <v>95234103.821871102</v>
       </c>
     </row>
@@ -21143,19 +21146,19 @@
         <v>424918533.51363516</v>
       </c>
       <c r="I477" s="246">
-        <f t="shared" ref="I477:L477" si="206">SUM(I473:I476)</f>
+        <f t="shared" ref="I477:L477" si="205">SUM(I473:I476)</f>
         <v>395382554.97087586</v>
       </c>
       <c r="J477" s="246">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>351658559.77577114</v>
       </c>
       <c r="K477" s="246">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>294472672.9960013</v>
       </c>
       <c r="L477" s="246">
-        <f t="shared" si="206"/>
+        <f t="shared" si="205"/>
         <v>224394186.03870523</v>
       </c>
     </row>
@@ -21218,15 +21221,15 @@
         <v>35500000</v>
       </c>
       <c r="J480" s="236">
-        <f t="shared" ref="J480:L480" si="207">I480-J479</f>
+        <f t="shared" ref="J480:L480" si="206">I480-J479</f>
         <v>35500000</v>
       </c>
       <c r="K480" s="236">
-        <f t="shared" si="207"/>
+        <f t="shared" si="206"/>
         <v>35500000</v>
       </c>
       <c r="L480" s="236">
-        <f t="shared" si="207"/>
+        <f t="shared" si="206"/>
         <v>35500000</v>
       </c>
     </row>
@@ -21245,19 +21248,19 @@
         <v>460418533.51363516</v>
       </c>
       <c r="I481" s="246">
-        <f t="shared" ref="I481:L481" si="208">I477+I480</f>
+        <f t="shared" ref="I481:L481" si="207">I477+I480</f>
         <v>430882554.97087586</v>
       </c>
       <c r="J481" s="246">
-        <f t="shared" si="208"/>
+        <f t="shared" si="207"/>
         <v>387158559.77577114</v>
       </c>
       <c r="K481" s="246">
-        <f t="shared" si="208"/>
+        <f t="shared" si="207"/>
         <v>329972672.9960013</v>
       </c>
       <c r="L481" s="246">
-        <f t="shared" si="208"/>
+        <f t="shared" si="207"/>
         <v>259894186.03870523</v>
       </c>
     </row>
@@ -21374,19 +21377,19 @@
         <v>2026</v>
       </c>
       <c r="I488" s="54">
-        <f t="shared" ref="I488" si="209">H488+1</f>
+        <f t="shared" ref="I488" si="208">H488+1</f>
         <v>2027</v>
       </c>
       <c r="J488" s="54">
-        <f t="shared" ref="J488" si="210">I488+1</f>
+        <f t="shared" ref="J488" si="209">I488+1</f>
         <v>2028</v>
       </c>
       <c r="K488" s="54">
-        <f t="shared" ref="K488" si="211">J488+1</f>
+        <f t="shared" ref="K488" si="210">J488+1</f>
         <v>2029</v>
       </c>
       <c r="L488" s="54">
-        <f t="shared" ref="L488" si="212">K488+1</f>
+        <f t="shared" ref="L488" si="211">K488+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -21531,11 +21534,11 @@
         <v>-80100000</v>
       </c>
       <c r="I495" s="236">
-        <f t="shared" ref="I495:L495" si="213">SUM(I564:I567)</f>
+        <f t="shared" ref="I495:L495" si="212">SUM(I564:I567)</f>
         <v>0</v>
       </c>
       <c r="J495" s="236">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
       <c r="K495" s="236">
@@ -21543,7 +21546,7 @@
         <v>-269700000</v>
       </c>
       <c r="L495" s="236">
-        <f t="shared" si="213"/>
+        <f t="shared" si="212"/>
         <v>0</v>
       </c>
     </row>
@@ -21562,19 +21565,19 @@
         <v>124099905.56847787</v>
       </c>
       <c r="I496" s="246">
-        <f t="shared" ref="I496:L496" si="214">SUM(I493:I495)</f>
+        <f t="shared" ref="I496:L496" si="213">SUM(I493:I495)</f>
         <v>-30923302.801395714</v>
       </c>
       <c r="J496" s="246">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>-108597661.856355</v>
       </c>
       <c r="K496" s="246">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>-368493089.74624586</v>
       </c>
       <c r="L496" s="246">
-        <f t="shared" si="214"/>
+        <f t="shared" si="213"/>
         <v>-82414759.579782978</v>
       </c>
     </row>
@@ -21633,19 +21636,19 @@
         <v>94099905.568477869</v>
       </c>
       <c r="I499" s="246">
-        <f t="shared" ref="I499:L499" si="215">I496-I498</f>
+        <f t="shared" ref="I499:L499" si="214">I496-I498</f>
         <v>-60923302.801395714</v>
       </c>
       <c r="J499" s="246">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>-138597661.85635501</v>
       </c>
       <c r="K499" s="246">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>-398493089.74624586</v>
       </c>
       <c r="L499" s="246">
-        <f t="shared" si="215"/>
+        <f t="shared" si="214"/>
         <v>-112414759.57978298</v>
       </c>
     </row>
@@ -21913,15 +21916,15 @@
         <v>0</v>
       </c>
       <c r="J511" s="236">
-        <f t="shared" ref="J511:L511" si="216">I514</f>
+        <f t="shared" ref="J511:L511" si="215">I514</f>
         <v>60923302.801395714</v>
       </c>
       <c r="K511" s="236">
-        <f t="shared" si="216"/>
+        <f t="shared" si="215"/>
         <v>87500000</v>
       </c>
       <c r="L511" s="236">
-        <f t="shared" si="216"/>
+        <f t="shared" si="215"/>
         <v>87500000</v>
       </c>
     </row>
@@ -21944,15 +21947,15 @@
         <v>60923302.801395714</v>
       </c>
       <c r="J512" s="236">
-        <f t="shared" ref="J512:L512" si="217">MIN(MAX(0, -J499), J517-J511)</f>
+        <f t="shared" ref="J512:L512" si="216">MIN(MAX(0, -J499), J517-J511)</f>
         <v>26576697.198604286</v>
       </c>
       <c r="K512" s="236">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>0</v>
       </c>
       <c r="L512" s="236">
-        <f t="shared" si="217"/>
+        <f t="shared" si="216"/>
         <v>0</v>
       </c>
     </row>
@@ -21975,15 +21978,15 @@
         <v>0</v>
       </c>
       <c r="J513" s="236">
-        <f t="shared" ref="J513:L513" si="218">J502</f>
+        <f t="shared" ref="J513:L513" si="217">J502</f>
         <v>0</v>
       </c>
       <c r="K513" s="236">
-        <f t="shared" si="218"/>
+        <f t="shared" si="217"/>
         <v>0</v>
       </c>
       <c r="L513" s="236">
-        <f t="shared" si="218"/>
+        <f t="shared" si="217"/>
         <v>0</v>
       </c>
     </row>
@@ -22002,19 +22005,19 @@
         <v>0</v>
       </c>
       <c r="I514" s="246">
-        <f t="shared" ref="I514:L514" si="219">SUM(I511:I513)</f>
+        <f t="shared" ref="I514:L514" si="218">SUM(I511:I513)</f>
         <v>60923302.801395714</v>
       </c>
       <c r="J514" s="246">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>87500000</v>
       </c>
       <c r="K514" s="246">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>87500000</v>
       </c>
       <c r="L514" s="246">
-        <f t="shared" si="219"/>
+        <f t="shared" si="218"/>
         <v>87500000</v>
       </c>
     </row>
@@ -22065,19 +22068,19 @@
         <v>87500000</v>
       </c>
       <c r="I517" s="236">
-        <f t="shared" ref="I517:L517" si="220">H517</f>
+        <f t="shared" ref="I517:L517" si="219">H517</f>
         <v>87500000</v>
       </c>
       <c r="J517" s="236">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>87500000</v>
       </c>
       <c r="K517" s="236">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>87500000</v>
       </c>
       <c r="L517" s="236">
-        <f t="shared" si="220"/>
+        <f t="shared" si="219"/>
         <v>87500000</v>
       </c>
     </row>
@@ -22099,19 +22102,19 @@
         <v>87500000</v>
       </c>
       <c r="I518" s="236">
-        <f t="shared" ref="I518:L518" si="221">I517-I514</f>
+        <f t="shared" ref="I518:L518" si="220">I517-I514</f>
         <v>26576697.198604286</v>
       </c>
       <c r="J518" s="236">
-        <f t="shared" si="221"/>
+        <f t="shared" si="220"/>
         <v>0</v>
       </c>
       <c r="K518" s="236">
-        <f t="shared" si="221"/>
+        <f t="shared" si="220"/>
         <v>0</v>
       </c>
       <c r="L518" s="236">
-        <f t="shared" si="221"/>
+        <f t="shared" si="220"/>
         <v>0</v>
       </c>
     </row>
@@ -22164,15 +22167,15 @@
         <v>150000000</v>
       </c>
       <c r="J521" s="236">
-        <f t="shared" ref="J521:L521" si="222">I521</f>
+        <f t="shared" ref="J521:L521" si="221">I521</f>
         <v>150000000</v>
       </c>
       <c r="K521" s="236">
-        <f t="shared" si="222"/>
+        <f t="shared" si="221"/>
         <v>150000000</v>
       </c>
       <c r="L521" s="236">
-        <f t="shared" si="222"/>
+        <f t="shared" si="221"/>
         <v>150000000</v>
       </c>
     </row>
@@ -22216,19 +22219,19 @@
         <v>-153800000</v>
       </c>
       <c r="I523" s="312">
-        <f t="shared" ref="I523:L523" si="223">I564</f>
+        <f t="shared" ref="I523:L523" si="222">I564</f>
         <v>0</v>
       </c>
       <c r="J523" s="312">
-        <f t="shared" si="223"/>
+        <f t="shared" si="222"/>
         <v>0</v>
       </c>
       <c r="K523" s="312">
-        <f t="shared" si="223"/>
+        <f t="shared" si="222"/>
         <v>0</v>
       </c>
       <c r="L523" s="312">
-        <f t="shared" si="223"/>
+        <f t="shared" si="222"/>
         <v>0</v>
       </c>
     </row>
@@ -22275,19 +22278,19 @@
         <v>150000000</v>
       </c>
       <c r="I525" s="246">
-        <f t="shared" ref="I525:L525" si="224">SUM(I521:I524)</f>
+        <f t="shared" ref="I525:L525" si="223">SUM(I521:I524)</f>
         <v>150000000</v>
       </c>
       <c r="J525" s="246">
-        <f t="shared" si="224"/>
+        <f t="shared" si="223"/>
         <v>150000000</v>
       </c>
       <c r="K525" s="246">
-        <f t="shared" si="224"/>
+        <f t="shared" si="223"/>
         <v>150000000</v>
       </c>
       <c r="L525" s="246">
-        <f t="shared" si="224"/>
+        <f t="shared" si="223"/>
         <v>150000000</v>
       </c>
     </row>
@@ -22340,15 +22343,15 @@
         <v>0</v>
       </c>
       <c r="J528" s="236">
-        <f t="shared" ref="J528:L528" si="225">I531</f>
+        <f t="shared" ref="J528:L528" si="224">I531</f>
         <v>0</v>
       </c>
       <c r="K528" s="236">
-        <f t="shared" si="225"/>
+        <f t="shared" si="224"/>
         <v>0</v>
       </c>
       <c r="L528" s="236">
-        <f t="shared" si="225"/>
+        <f t="shared" si="224"/>
         <v>0</v>
       </c>
     </row>
@@ -22367,19 +22370,19 @@
         <v>-6500000</v>
       </c>
       <c r="I529" s="382">
-        <f t="shared" ref="I529:L529" si="226">I565</f>
+        <f t="shared" ref="I529:L529" si="225">I565</f>
         <v>0</v>
       </c>
       <c r="J529" s="382">
-        <f t="shared" si="226"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="K529" s="382">
-        <f t="shared" si="226"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
       <c r="L529" s="382">
-        <f t="shared" si="226"/>
+        <f t="shared" si="225"/>
         <v>0</v>
       </c>
     </row>
@@ -22426,19 +22429,19 @@
         <v>0</v>
       </c>
       <c r="I531" s="246">
-        <f t="shared" ref="I531:L531" si="227">SUM(I528:I530)</f>
+        <f t="shared" ref="I531:L531" si="226">SUM(I528:I530)</f>
         <v>0</v>
       </c>
       <c r="J531" s="246">
-        <f t="shared" si="227"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="K531" s="246">
-        <f t="shared" si="227"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
       <c r="L531" s="246">
-        <f t="shared" si="227"/>
+        <f t="shared" si="226"/>
         <v>0</v>
       </c>
     </row>
@@ -22491,15 +22494,15 @@
         <v>0</v>
       </c>
       <c r="J534" s="236">
-        <f t="shared" ref="J534:L534" si="228">I537</f>
+        <f t="shared" ref="J534:L534" si="227">I537</f>
         <v>0</v>
       </c>
       <c r="K534" s="236">
-        <f t="shared" si="228"/>
+        <f t="shared" si="227"/>
         <v>0</v>
       </c>
       <c r="L534" s="236">
-        <f t="shared" si="228"/>
+        <f t="shared" si="227"/>
         <v>0</v>
       </c>
     </row>
@@ -22518,19 +22521,19 @@
         <v>-73600000</v>
       </c>
       <c r="I535" s="382">
-        <f t="shared" ref="I535:L535" si="229">I566</f>
+        <f t="shared" ref="I535:L535" si="228">I566</f>
         <v>0</v>
       </c>
       <c r="J535" s="382">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>0</v>
       </c>
       <c r="K535" s="382">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>0</v>
       </c>
       <c r="L535" s="382">
-        <f t="shared" si="229"/>
+        <f t="shared" si="228"/>
         <v>0</v>
       </c>
     </row>
@@ -22577,19 +22580,19 @@
         <v>0</v>
       </c>
       <c r="I537" s="246">
-        <f t="shared" ref="I537:L537" si="230">SUM(I534:I536)</f>
+        <f t="shared" ref="I537:L537" si="229">SUM(I534:I536)</f>
         <v>0</v>
       </c>
       <c r="J537" s="246">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>0</v>
       </c>
       <c r="K537" s="246">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>0</v>
       </c>
       <c r="L537" s="246">
-        <f t="shared" si="230"/>
+        <f t="shared" si="229"/>
         <v>0</v>
       </c>
     </row>
@@ -22642,15 +22645,15 @@
         <v>269700000</v>
       </c>
       <c r="J540" s="236">
-        <f t="shared" ref="J540:L540" si="231">I543</f>
+        <f t="shared" ref="J540:L540" si="230">I543</f>
         <v>269700000</v>
       </c>
       <c r="K540" s="236">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>269700000</v>
       </c>
       <c r="L540" s="236">
-        <f t="shared" si="231"/>
+        <f t="shared" si="230"/>
         <v>0</v>
       </c>
     </row>
@@ -22669,19 +22672,19 @@
         <v>0</v>
       </c>
       <c r="I541" s="382">
-        <f t="shared" ref="I541:L541" si="232">I567</f>
+        <f t="shared" ref="I541:L541" si="231">I567</f>
         <v>0</v>
       </c>
       <c r="J541" s="382">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0</v>
       </c>
       <c r="K541" s="382">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>-269700000</v>
       </c>
       <c r="L541" s="382">
-        <f t="shared" si="232"/>
+        <f t="shared" si="231"/>
         <v>0</v>
       </c>
     </row>
@@ -22728,19 +22731,19 @@
         <v>269700000</v>
       </c>
       <c r="I543" s="246">
-        <f t="shared" ref="I543:L543" si="233">SUM(I540:I542)</f>
+        <f t="shared" ref="I543:L543" si="232">SUM(I540:I542)</f>
         <v>269700000</v>
       </c>
       <c r="J543" s="246">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>269700000</v>
       </c>
       <c r="K543" s="246">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>0</v>
       </c>
       <c r="L543" s="246">
-        <f t="shared" si="233"/>
+        <f t="shared" si="232"/>
         <v>0</v>
       </c>
     </row>
@@ -22789,19 +22792,19 @@
         <v>244099905.56847787</v>
       </c>
       <c r="I546" s="236">
-        <f t="shared" ref="I546:L546" si="234">I499+I512+I522-I524-I530-I536-I542</f>
+        <f t="shared" ref="I546:L546" si="233">I499+I512+I522-I524-I530-I536-I542</f>
         <v>0</v>
       </c>
       <c r="J546" s="236">
-        <f t="shared" si="234"/>
+        <f t="shared" si="233"/>
         <v>-112020964.65775073</v>
       </c>
       <c r="K546" s="236">
-        <f t="shared" si="234"/>
+        <f t="shared" si="233"/>
         <v>-398493089.74624586</v>
       </c>
       <c r="L546" s="236">
-        <f t="shared" si="234"/>
+        <f t="shared" si="233"/>
         <v>-112414759.57978298</v>
       </c>
     </row>
@@ -22820,19 +22823,19 @@
         <v>0</v>
       </c>
       <c r="I547" s="236">
-        <f t="shared" ref="I547:L547" si="235">MAX(-I546, 0)</f>
+        <f t="shared" ref="I547:L547" si="234">MAX(-I546, 0)</f>
         <v>0</v>
       </c>
       <c r="J547" s="236">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>112020964.65775073</v>
       </c>
       <c r="K547" s="236">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>398493089.74624586</v>
       </c>
       <c r="L547" s="236">
-        <f t="shared" si="235"/>
+        <f t="shared" si="234"/>
         <v>112414759.57978298</v>
       </c>
     </row>
@@ -22885,15 +22888,15 @@
         <v>0</v>
       </c>
       <c r="J550" s="236">
-        <f t="shared" ref="J550" si="236">I553</f>
+        <f t="shared" ref="J550" si="235">I553</f>
         <v>0</v>
       </c>
       <c r="K550" s="236">
-        <f t="shared" ref="K550" si="237">J553</f>
+        <f t="shared" ref="K550" si="236">J553</f>
         <v>112020964.65775073</v>
       </c>
       <c r="L550" s="236">
-        <f t="shared" ref="L550" si="238">K553</f>
+        <f t="shared" ref="L550" si="237">K553</f>
         <v>510514054.40399659</v>
       </c>
     </row>
@@ -22912,19 +22915,19 @@
         <v>0</v>
       </c>
       <c r="I551" s="382">
-        <f t="shared" ref="I551:L551" si="239">I547</f>
+        <f t="shared" ref="I551:L551" si="238">I547</f>
         <v>0</v>
       </c>
       <c r="J551" s="382">
-        <f t="shared" si="239"/>
+        <f t="shared" si="238"/>
         <v>112020964.65775073</v>
       </c>
       <c r="K551" s="382">
-        <f t="shared" si="239"/>
+        <f t="shared" si="238"/>
         <v>398493089.74624586</v>
       </c>
       <c r="L551" s="382">
-        <f t="shared" si="239"/>
+        <f t="shared" si="238"/>
         <v>112414759.57978298</v>
       </c>
     </row>
@@ -22971,19 +22974,19 @@
         <v>0</v>
       </c>
       <c r="I553" s="246">
-        <f t="shared" ref="I553:L553" si="240">SUM(I550:I552)</f>
+        <f t="shared" ref="I553:L553" si="239">SUM(I550:I552)</f>
         <v>0</v>
       </c>
       <c r="J553" s="246">
-        <f t="shared" si="240"/>
+        <f t="shared" si="239"/>
         <v>112020964.65775073</v>
       </c>
       <c r="K553" s="246">
-        <f t="shared" si="240"/>
+        <f t="shared" si="239"/>
         <v>510514054.40399659</v>
       </c>
       <c r="L553" s="246">
-        <f t="shared" si="240"/>
+        <f t="shared" si="239"/>
         <v>622928813.98377955</v>
       </c>
     </row>
@@ -23036,15 +23039,15 @@
         <v>419700000</v>
       </c>
       <c r="J556" s="236">
-        <f t="shared" ref="J556:L556" si="241">I560</f>
+        <f t="shared" ref="J556:L556" si="240">I560</f>
         <v>480623302.80139571</v>
       </c>
       <c r="K556" s="236">
-        <f t="shared" si="241"/>
+        <f t="shared" si="240"/>
         <v>619220964.65775073</v>
       </c>
       <c r="L556" s="236">
-        <f t="shared" si="241"/>
+        <f t="shared" si="240"/>
         <v>748014054.40399659</v>
       </c>
     </row>
@@ -23067,15 +23070,15 @@
         <v>60923302.801395714</v>
       </c>
       <c r="J557" s="236">
-        <f t="shared" ref="J557:L557" si="242">J512+J522+J551</f>
+        <f t="shared" ref="J557:L557" si="241">J512+J522+J551</f>
         <v>138597661.85635501</v>
       </c>
       <c r="K557" s="236">
-        <f t="shared" si="242"/>
+        <f t="shared" si="241"/>
         <v>398493089.74624586</v>
       </c>
       <c r="L557" s="236">
-        <f t="shared" si="242"/>
+        <f t="shared" si="241"/>
         <v>112414759.57978298</v>
       </c>
     </row>
@@ -23094,19 +23097,19 @@
         <v>-233900000</v>
       </c>
       <c r="I558" s="382">
-        <f t="shared" ref="I558:L558" si="243">I513+I523+I529+I535+I541+I552</f>
+        <f t="shared" ref="I558:L558" si="242">I513+I523+I529+I535+I541+I552</f>
         <v>0</v>
       </c>
       <c r="J558" s="382">
-        <f t="shared" si="243"/>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
       <c r="K558" s="382">
-        <f t="shared" si="243"/>
+        <f t="shared" si="242"/>
         <v>-269700000</v>
       </c>
       <c r="L558" s="382">
-        <f t="shared" si="243"/>
+        <f t="shared" si="242"/>
         <v>0</v>
       </c>
     </row>
@@ -23125,19 +23128,19 @@
         <v>0</v>
       </c>
       <c r="I559" s="180">
-        <f t="shared" ref="I559:L559" si="244">I524+I530+I536+I542</f>
+        <f t="shared" ref="I559:L559" si="243">I524+I530+I536+I542</f>
         <v>0</v>
       </c>
       <c r="J559" s="180">
-        <f t="shared" si="244"/>
+        <f t="shared" si="243"/>
         <v>0</v>
       </c>
       <c r="K559" s="180">
-        <f t="shared" si="244"/>
+        <f t="shared" si="243"/>
         <v>0</v>
       </c>
       <c r="L559" s="180">
-        <f t="shared" si="244"/>
+        <f t="shared" si="243"/>
         <v>0</v>
       </c>
     </row>
@@ -23158,19 +23161,19 @@
         <v>419700000</v>
       </c>
       <c r="I560" s="246">
-        <f t="shared" ref="I560:L560" si="245">SUM(I556:I559)</f>
+        <f t="shared" ref="I560:L560" si="244">SUM(I556:I559)</f>
         <v>480623302.80139571</v>
       </c>
       <c r="J560" s="246">
-        <f t="shared" si="245"/>
+        <f t="shared" si="244"/>
         <v>619220964.65775073</v>
       </c>
       <c r="K560" s="246">
-        <f t="shared" si="245"/>
+        <f t="shared" si="244"/>
         <v>748014054.40399659</v>
       </c>
       <c r="L560" s="246">
-        <f t="shared" si="245"/>
+        <f t="shared" si="244"/>
         <v>860428813.98377955</v>
       </c>
     </row>
@@ -23408,15 +23411,15 @@
         <v>0.01</v>
       </c>
       <c r="J572" s="385">
-        <f t="shared" ref="J572:L572" si="246">I572</f>
+        <f t="shared" ref="J572:L572" si="245">I572</f>
         <v>0.01</v>
       </c>
       <c r="K572" s="385">
-        <f t="shared" si="246"/>
+        <f t="shared" si="245"/>
         <v>0.01</v>
       </c>
       <c r="L572" s="385">
-        <f t="shared" si="246"/>
+        <f t="shared" si="245"/>
         <v>0.01</v>
       </c>
     </row>
@@ -23438,15 +23441,15 @@
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="J573" s="387">
-        <f t="shared" ref="J573:L573" si="247">I573</f>
+        <f t="shared" ref="J573:L573" si="246">I573</f>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="K573" s="387">
-        <f t="shared" si="247"/>
+        <f t="shared" si="246"/>
         <v>5.0000000000000001E-3</v>
       </c>
       <c r="L573" s="387">
-        <f t="shared" si="247"/>
+        <f t="shared" si="246"/>
         <v>5.0000000000000001E-3</v>
       </c>
     </row>
@@ -23985,19 +23988,19 @@
         <v>48304600</v>
       </c>
       <c r="I594" s="225">
-        <f t="shared" ref="I594:L594" si="248">I583+SUM(I585:I590)</f>
+        <f t="shared" ref="I594:L594" si="247">I583+SUM(I585:I590)</f>
         <v>47504500</v>
       </c>
       <c r="J594" s="225">
-        <f t="shared" si="248"/>
+        <f t="shared" si="247"/>
         <v>53892213.766132593</v>
       </c>
       <c r="K594" s="225">
-        <f t="shared" si="248"/>
+        <f t="shared" si="247"/>
         <v>69859515.758930087</v>
       </c>
       <c r="L594" s="225">
-        <f t="shared" si="248"/>
+        <f t="shared" si="247"/>
         <v>85767644.365267605</v>
       </c>
     </row>
@@ -24467,19 +24470,19 @@
         <v>2026</v>
       </c>
       <c r="I616" s="54">
-        <f t="shared" ref="I616" si="249">H616+1</f>
+        <f t="shared" ref="I616" si="248">H616+1</f>
         <v>2027</v>
       </c>
       <c r="J616" s="54">
-        <f t="shared" ref="J616" si="250">I616+1</f>
+        <f t="shared" ref="J616" si="249">I616+1</f>
         <v>2028</v>
       </c>
       <c r="K616" s="54">
-        <f t="shared" ref="K616" si="251">J616+1</f>
+        <f t="shared" ref="K616" si="250">J616+1</f>
         <v>2029</v>
       </c>
       <c r="L616" s="54">
-        <f t="shared" ref="L616" si="252">K616+1</f>
+        <f t="shared" ref="L616" si="251">K616+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -24978,19 +24981,19 @@
         <v>2026</v>
       </c>
       <c r="I641" s="54">
-        <f t="shared" ref="I641" si="253">H641+1</f>
+        <f t="shared" ref="I641" si="252">H641+1</f>
         <v>2027</v>
       </c>
       <c r="J641" s="54">
-        <f t="shared" ref="J641" si="254">I641+1</f>
+        <f t="shared" ref="J641" si="253">I641+1</f>
         <v>2028</v>
       </c>
       <c r="K641" s="54">
-        <f t="shared" ref="K641" si="255">J641+1</f>
+        <f t="shared" ref="K641" si="254">J641+1</f>
         <v>2029</v>
       </c>
       <c r="L641" s="54">
-        <f t="shared" ref="L641" si="256">K641+1</f>
+        <f t="shared" ref="L641" si="255">K641+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -25067,31 +25070,31 @@
       <c r="D646" s="61"/>
       <c r="E646" s="61"/>
       <c r="F646" s="180">
-        <f t="shared" ref="F646:L646" si="257">F31</f>
+        <f t="shared" ref="F646:L646" si="256">F31</f>
         <v>-379300000</v>
       </c>
       <c r="G646" s="180">
-        <f t="shared" si="257"/>
+        <f t="shared" si="256"/>
         <v>-281600000</v>
       </c>
       <c r="H646" s="236">
-        <f t="shared" si="257"/>
+        <f t="shared" si="256"/>
         <v>-165041562.09016538</v>
       </c>
       <c r="I646" s="236">
-        <f t="shared" si="257"/>
+        <f t="shared" si="256"/>
         <v>-182239030.44808081</v>
       </c>
       <c r="J646" s="236">
-        <f t="shared" si="257"/>
+        <f t="shared" si="256"/>
         <v>-193316137.6387279</v>
       </c>
       <c r="K646" s="236">
-        <f t="shared" si="257"/>
+        <f t="shared" si="256"/>
         <v>-203235424.54314363</v>
       </c>
       <c r="L646" s="236">
-        <f t="shared" si="257"/>
+        <f t="shared" si="256"/>
         <v>-206177531.09173626</v>
       </c>
     </row>
@@ -25243,19 +25246,19 @@
         <v>0</v>
       </c>
       <c r="I652" s="246">
-        <f t="shared" ref="I652:L652" si="258">MAX(I649, I649-I651)</f>
+        <f t="shared" ref="I652:L652" si="257">MAX(I649, I649-I651)</f>
         <v>0</v>
       </c>
       <c r="J652" s="246">
-        <f t="shared" si="258"/>
+        <f t="shared" si="257"/>
         <v>0</v>
       </c>
       <c r="K652" s="246">
-        <f t="shared" si="258"/>
+        <f t="shared" si="257"/>
         <v>0</v>
       </c>
       <c r="L652" s="246">
-        <f t="shared" si="258"/>
+        <f t="shared" si="257"/>
         <v>0</v>
       </c>
     </row>
@@ -25380,19 +25383,19 @@
         <v>3700000</v>
       </c>
       <c r="I658" s="246">
-        <f t="shared" ref="I658:L658" si="259">SUM(I656:I657)</f>
+        <f t="shared" ref="I658:L658" si="258">SUM(I656:I657)</f>
         <v>3700000</v>
       </c>
       <c r="J658" s="246">
-        <f t="shared" si="259"/>
+        <f t="shared" si="258"/>
         <v>3700000</v>
       </c>
       <c r="K658" s="246">
-        <f t="shared" si="259"/>
+        <f t="shared" si="258"/>
         <v>3700000</v>
       </c>
       <c r="L658" s="246">
-        <f t="shared" si="259"/>
+        <f t="shared" si="258"/>
         <v>3700000</v>
       </c>
     </row>
@@ -25425,19 +25428,19 @@
         <v>3700000</v>
       </c>
       <c r="I660" s="236">
-        <f t="shared" ref="I660:L660" si="260">I658</f>
+        <f t="shared" ref="I660:L660" si="259">I658</f>
         <v>3700000</v>
       </c>
       <c r="J660" s="236">
-        <f t="shared" si="260"/>
+        <f t="shared" si="259"/>
         <v>3700000</v>
       </c>
       <c r="K660" s="236">
-        <f t="shared" si="260"/>
+        <f t="shared" si="259"/>
         <v>3700000</v>
       </c>
       <c r="L660" s="236">
-        <f t="shared" si="260"/>
+        <f t="shared" si="259"/>
         <v>3700000</v>
       </c>
     </row>
@@ -25456,19 +25459,19 @@
         <v>0</v>
       </c>
       <c r="I661" s="236">
-        <f t="shared" ref="I661:L661" si="261">I649</f>
+        <f t="shared" ref="I661:L661" si="260">I649</f>
         <v>0</v>
       </c>
       <c r="J661" s="236">
-        <f t="shared" si="261"/>
+        <f t="shared" si="260"/>
         <v>0</v>
       </c>
       <c r="K661" s="236">
-        <f t="shared" si="261"/>
+        <f t="shared" si="260"/>
         <v>0</v>
       </c>
       <c r="L661" s="236">
-        <f t="shared" si="261"/>
+        <f t="shared" si="260"/>
         <v>0</v>
       </c>
     </row>
@@ -25487,19 +25490,19 @@
         <v>0</v>
       </c>
       <c r="I662" s="236">
-        <f t="shared" ref="I662:L662" si="262">-I652</f>
+        <f t="shared" ref="I662:L662" si="261">-I652</f>
         <v>0</v>
       </c>
       <c r="J662" s="236">
-        <f t="shared" si="262"/>
+        <f t="shared" si="261"/>
         <v>0</v>
       </c>
       <c r="K662" s="236">
-        <f t="shared" si="262"/>
+        <f t="shared" si="261"/>
         <v>0</v>
       </c>
       <c r="L662" s="236">
-        <f t="shared" si="262"/>
+        <f t="shared" si="261"/>
         <v>0</v>
       </c>
     </row>
@@ -25518,19 +25521,19 @@
         <v>3700000</v>
       </c>
       <c r="I663" s="246">
-        <f t="shared" ref="I663:L663" si="263">SUM(I660:I662)</f>
+        <f t="shared" ref="I663:L663" si="262">SUM(I660:I662)</f>
         <v>3700000</v>
       </c>
       <c r="J663" s="246">
-        <f t="shared" si="263"/>
+        <f t="shared" si="262"/>
         <v>3700000</v>
       </c>
       <c r="K663" s="246">
-        <f t="shared" si="263"/>
+        <f t="shared" si="262"/>
         <v>3700000</v>
       </c>
       <c r="L663" s="246">
-        <f t="shared" si="263"/>
+        <f t="shared" si="262"/>
         <v>3700000</v>
       </c>
     </row>
@@ -25563,19 +25566,19 @@
         <v>3700000</v>
       </c>
       <c r="I665" s="246">
-        <f t="shared" ref="I665:L665" si="264">IF(I663&gt;0, I663, 0)</f>
+        <f t="shared" ref="I665:L665" si="263">IF(I663&gt;0, I663, 0)</f>
         <v>3700000</v>
       </c>
       <c r="J665" s="246">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>3700000</v>
       </c>
       <c r="K665" s="246">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>3700000</v>
       </c>
       <c r="L665" s="246">
-        <f t="shared" si="264"/>
+        <f t="shared" si="263"/>
         <v>3700000</v>
       </c>
     </row>
@@ -25594,19 +25597,19 @@
         <v>0</v>
       </c>
       <c r="I666" s="246">
-        <f t="shared" ref="I666:L666" si="265">IF(I663&lt;0, I663, 0)</f>
+        <f t="shared" ref="I666:L666" si="264">IF(I663&lt;0, I663, 0)</f>
         <v>0</v>
       </c>
       <c r="J666" s="246">
-        <f t="shared" si="265"/>
+        <f t="shared" si="264"/>
         <v>0</v>
       </c>
       <c r="K666" s="246">
-        <f t="shared" si="265"/>
+        <f t="shared" si="264"/>
         <v>0</v>
       </c>
       <c r="L666" s="246">
-        <f t="shared" si="265"/>
+        <f t="shared" si="264"/>
         <v>0</v>
       </c>
     </row>
@@ -25885,19 +25888,19 @@
         <v>2026</v>
       </c>
       <c r="I681" s="54">
-        <f t="shared" ref="I681" si="266">H681+1</f>
+        <f t="shared" ref="I681" si="265">H681+1</f>
         <v>2027</v>
       </c>
       <c r="J681" s="54">
-        <f t="shared" ref="J681" si="267">I681+1</f>
+        <f t="shared" ref="J681" si="266">I681+1</f>
         <v>2028</v>
       </c>
       <c r="K681" s="54">
-        <f t="shared" ref="K681" si="268">J681+1</f>
+        <f t="shared" ref="K681" si="267">J681+1</f>
         <v>2029</v>
       </c>
       <c r="L681" s="54">
-        <f t="shared" ref="L681" si="269">K681+1</f>
+        <f t="shared" ref="L681" si="268">K681+1</f>
         <v>2030</v>
       </c>
     </row>
@@ -26030,19 +26033,19 @@
         <v>0</v>
       </c>
       <c r="I688" s="246">
-        <f t="shared" ref="I688:L688" si="270">MAX(I687*I686, 0)</f>
+        <f t="shared" ref="I688:L688" si="269">MAX(I687*I686, 0)</f>
         <v>0</v>
       </c>
       <c r="J688" s="246">
-        <f t="shared" si="270"/>
+        <f t="shared" si="269"/>
         <v>0</v>
       </c>
       <c r="K688" s="246">
-        <f t="shared" si="270"/>
+        <f t="shared" si="269"/>
         <v>0</v>
       </c>
       <c r="L688" s="246">
-        <f t="shared" si="270"/>
+        <f t="shared" si="269"/>
         <v>0</v>
       </c>
     </row>
@@ -26101,19 +26104,19 @@
         <v>-118000000</v>
       </c>
       <c r="I692" s="236">
-        <f t="shared" ref="I692:L692" si="271">H697</f>
+        <f t="shared" ref="I692:L692" si="270">H697</f>
         <v>-283041562.09016538</v>
       </c>
       <c r="J692" s="236">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>-465280592.53824615</v>
       </c>
       <c r="K692" s="236">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>-658596730.17697406</v>
       </c>
       <c r="L692" s="236">
-        <f t="shared" si="271"/>
+        <f t="shared" si="270"/>
         <v>-861832154.72011769</v>
       </c>
     </row>
@@ -26161,19 +26164,19 @@
         <v>0</v>
       </c>
       <c r="I694" s="236">
-        <f t="shared" ref="I694:L694" si="272">-I688</f>
+        <f t="shared" ref="I694:L694" si="271">-I688</f>
         <v>0</v>
       </c>
       <c r="J694" s="236">
-        <f t="shared" si="272"/>
+        <f t="shared" si="271"/>
         <v>0</v>
       </c>
       <c r="K694" s="236">
-        <f t="shared" si="272"/>
+        <f t="shared" si="271"/>
         <v>0</v>
       </c>
       <c r="L694" s="236">
-        <f t="shared" si="272"/>
+        <f t="shared" si="271"/>
         <v>0</v>
       </c>
     </row>
@@ -26254,19 +26257,19 @@
         <v>-283041562.09016538</v>
       </c>
       <c r="I697" s="246">
-        <f t="shared" ref="I697:L697" si="273">SUM(I692:I696)</f>
+        <f t="shared" ref="I697:L697" si="272">SUM(I692:I696)</f>
         <v>-465280592.53824615</v>
       </c>
       <c r="J697" s="246">
-        <f t="shared" si="273"/>
+        <f t="shared" si="272"/>
         <v>-658596730.17697406</v>
       </c>
       <c r="K697" s="246">
-        <f t="shared" si="273"/>
+        <f t="shared" si="272"/>
         <v>-861832154.72011769</v>
       </c>
       <c r="L697" s="246">
-        <f t="shared" si="273"/>
+        <f t="shared" si="272"/>
         <v>-1068009685.8118539</v>
       </c>
     </row>
@@ -28143,24 +28146,24 @@
       <c r="D12" s="61"/>
       <c r="E12" s="61"/>
       <c r="F12" s="275">
-        <f>Model!H647</f>
-        <v>0.25</v>
+        <f>IF(F11&lt;0, 0, Model!H647)</f>
+        <v>0</v>
       </c>
       <c r="G12" s="275">
-        <f>Model!I647</f>
-        <v>0.25</v>
+        <f>IF(G11&lt;0, 0, Model!I647)</f>
+        <v>0</v>
       </c>
       <c r="H12" s="275">
-        <f>Model!J647</f>
-        <v>0.25</v>
+        <f>IF(H11&lt;0, 0, Model!J647)</f>
+        <v>0</v>
       </c>
       <c r="I12" s="275">
-        <f>Model!K647</f>
-        <v>0.25</v>
+        <f>IF(I11&lt;0, 0, Model!K647)</f>
+        <v>0</v>
       </c>
       <c r="J12" s="275">
-        <f>Model!L647</f>
-        <v>0.25</v>
+        <f>IF(J11&lt;0, 0, Model!L647)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -28172,23 +28175,23 @@
       <c r="E13" s="61"/>
       <c r="F13" s="236">
         <f>(1-F12)*F11</f>
-        <v>-84893221.567624032</v>
+        <v>-113190962.09016538</v>
       </c>
       <c r="G13" s="236">
         <f t="shared" ref="G13:J13" si="1">(1-G12)*G11</f>
-        <v>-97472609.627824187</v>
+        <v>-129963479.50376558</v>
       </c>
       <c r="H13" s="236">
         <f t="shared" si="1"/>
-        <v>-100900239.27944648</v>
+        <v>-134533652.37259531</v>
       </c>
       <c r="I13" s="236">
         <f t="shared" si="1"/>
-        <v>-96969696.854410172</v>
+        <v>-129292929.13921356</v>
       </c>
       <c r="J13" s="236">
         <f t="shared" si="1"/>
-        <v>-87868813.269088984</v>
+        <v>-117158417.69211864</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -28284,23 +28287,23 @@
       <c r="E17" s="185"/>
       <c r="F17" s="264">
         <f>SUM(F13:F15)-F16</f>
-        <v>9851507.9020428509</v>
+        <v>-18446232.620498493</v>
       </c>
       <c r="G17" s="264">
         <f t="shared" ref="G17:J17" si="2">SUM(G13:G15)-G16</f>
-        <v>-34368422.195286244</v>
+        <v>-66859292.07122764</v>
       </c>
       <c r="H17" s="264">
         <f t="shared" si="2"/>
-        <v>-13309619.642742902</v>
+        <v>-46943032.73589173</v>
       </c>
       <c r="I17" s="264">
         <f t="shared" si="2"/>
-        <v>11152073.651818261</v>
+        <v>-21171158.63298513</v>
       </c>
       <c r="J17" s="264">
         <f t="shared" si="2"/>
-        <v>40404904.562844992</v>
+        <v>11115300.139815331</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -28426,7 +28429,7 @@
       </c>
       <c r="J26" s="236">
         <f>SUMPRODUCT(F17:J17,F18:J18)</f>
-        <v>1894003.1505891718</v>
+        <v>-110171253.0543559</v>
       </c>
     </row>
     <row r="27" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -28443,8 +28446,8 @@
         <v>419</v>
       </c>
       <c r="J27" s="236">
-        <f>J17*(1+J24)/(J24-J25)</f>
-        <v>473045187.6360662</v>
+        <f>J17*(1+J25)/(J24-J25)</f>
+        <v>119018387.76660913</v>
       </c>
     </row>
     <row r="28" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -28462,7 +28465,7 @@
       </c>
       <c r="J28" s="236">
         <f>J18*J27</f>
-        <v>267549983.58680326</v>
+        <v>67315699.484469801</v>
       </c>
     </row>
     <row r="29" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -28481,7 +28484,7 @@
       <c r="I29" s="232"/>
       <c r="J29" s="228">
         <f>J26+J28</f>
-        <v>269443986.73739243</v>
+        <v>-42855553.569886103</v>
       </c>
     </row>
     <row r="30" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -28517,7 +28520,7 @@
       <c r="I31" s="210"/>
       <c r="J31" s="228">
         <f>J29-J30</f>
-        <v>-229091107.69412971</v>
+        <v>-541390648.00140822</v>
       </c>
     </row>
     <row r="32" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -28665,8 +28668,8 @@
         <v>378</v>
       </c>
       <c r="F13" s="236">
-        <f>(F11*F10)+F12</f>
-        <v>645078889.53392494</v>
+        <f>F10*F11</f>
+        <v>146543795.10240278</v>
       </c>
     </row>
     <row r="14" spans="2:9" x14ac:dyDescent="0.3">
@@ -28690,7 +28693,7 @@
         <v>371</v>
       </c>
       <c r="F16" s="236">
-        <f>F13</f>
+        <f>SUM(F12:F13)</f>
         <v>645078889.53392494</v>
       </c>
     </row>
@@ -28814,8 +28817,8 @@
         <v>390</v>
       </c>
       <c r="F30" s="236">
-        <f>'LBO Debt'!J21</f>
-        <v>-69340961.632640377</v>
+        <f>'LBO Debt'!J22</f>
+        <v>253092903.83498985</v>
       </c>
     </row>
     <row r="32" spans="2:9" ht="15" x14ac:dyDescent="0.35">
@@ -28827,7 +28830,7 @@
       <c r="E32" s="232"/>
       <c r="F32" s="303">
         <f>F29-F30</f>
-        <v>756935176.88704944</v>
+        <v>434501311.41941923</v>
       </c>
     </row>
     <row r="33" spans="2:6" ht="15" x14ac:dyDescent="0.35">
@@ -28839,7 +28842,7 @@
       <c r="E33" s="232"/>
       <c r="F33" s="308">
         <f>F32/F22</f>
-        <v>1.2823224116917444</v>
+        <v>0.73608782701047182</v>
       </c>
     </row>
     <row r="34" spans="2:6" ht="15" x14ac:dyDescent="0.35">
@@ -28851,7 +28854,7 @@
       <c r="E34" s="232"/>
       <c r="F34" s="309">
         <f>F33^(1/5)-1</f>
-        <v>5.0992087804351716E-2</v>
+        <v>-5.9441251899954306E-2</v>
       </c>
     </row>
     <row r="37" spans="2:6" ht="15" x14ac:dyDescent="0.35">
@@ -28918,7 +28921,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D99F3CF4-E302-44CB-BA79-AF83143FA5C8}">
-  <dimension ref="B2:J21"/>
+  <dimension ref="B2:J22"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="10" width="17.77734375" customWidth="1"/>
@@ -29040,20 +29043,20 @@
         <v>97695863.401601851</v>
       </c>
       <c r="G11" s="395">
-        <f>F19</f>
-        <v>64438826.279167116</v>
+        <f>F20</f>
+        <v>96718904.767585829</v>
       </c>
       <c r="H11" s="395">
-        <f t="shared" ref="H11:J11" si="1">G19</f>
-        <v>63794438.016375445</v>
+        <f t="shared" ref="H11:J11" si="1">G20</f>
+        <v>95751715.719909966</v>
       </c>
       <c r="I11" s="395">
         <f t="shared" si="1"/>
-        <v>51410182.22522369</v>
+        <v>94794198.562710866</v>
       </c>
       <c r="J11" s="395">
         <f t="shared" si="1"/>
-        <v>13728295.87360803</v>
+        <v>93846256.577083752</v>
       </c>
     </row>
     <row r="12" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -29066,19 +29069,19 @@
       </c>
       <c r="G12" s="396">
         <f>G11*LBO!$F$43</f>
-        <v>644388.26279167121</v>
+        <v>967189.04767585825</v>
       </c>
       <c r="H12" s="396">
         <f>H11*LBO!$F$43</f>
-        <v>637944.38016375445</v>
+        <v>957517.15719909966</v>
       </c>
       <c r="I12" s="396">
         <f>I11*LBO!$F$43</f>
-        <v>514101.82225223689</v>
+        <v>947941.98562710872</v>
       </c>
       <c r="J12" s="396">
         <f>J11*LBO!$F$43</f>
-        <v>137282.9587360803</v>
+        <v>938462.56577083748</v>
       </c>
     </row>
     <row r="13" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -29091,19 +29094,19 @@
       </c>
       <c r="G13" s="236">
         <f>G11*LBO!$F$42</f>
-        <v>5799494.3651250405</v>
+        <v>8704701.4290827252</v>
       </c>
       <c r="H13" s="236">
         <f>H11*LBO!$F$42</f>
-        <v>5741499.42147379</v>
+        <v>8617654.4147918969</v>
       </c>
       <c r="I13" s="236">
         <f>I11*LBO!$F$42</f>
-        <v>4626916.4002701323</v>
+        <v>8531477.8706439771</v>
       </c>
       <c r="J13" s="236">
         <f>J11*LBO!$F$42</f>
-        <v>1235546.6286247226</v>
+        <v>8446163.0919375382</v>
       </c>
     </row>
     <row r="14" spans="2:10" ht="15" x14ac:dyDescent="0.35">
@@ -29111,208 +29114,233 @@
         <v>401</v>
       </c>
       <c r="F14" s="236">
-        <f>F13*(1-Model!H647)</f>
-        <v>6594470.7796081249</v>
+        <f>IF(Model!F18&gt;0, F13*(1-Model!H647), F13)</f>
+        <v>8792627.7061441671</v>
       </c>
       <c r="G14" s="236">
-        <f>G13*(1-Model!I647)</f>
-        <v>4349620.7738437802</v>
+        <f>IF(Model!G18&gt;0, G13*(1-Model!I647), G13)</f>
+        <v>8704701.4290827252</v>
       </c>
       <c r="H14" s="236">
-        <f>H13*(1-Model!J647)</f>
-        <v>4306124.5661053425</v>
+        <f>IF(Model!H18&gt;0, H13*(1-Model!J647), H13)</f>
+        <v>8617654.4147918969</v>
       </c>
       <c r="I14" s="236">
-        <f>I13*(1-Model!K647)</f>
-        <v>3470187.3002025993</v>
+        <f>IF(Model!I18&gt;0, I13*(1-Model!K647), I13)</f>
+        <v>8531477.8706439771</v>
       </c>
       <c r="J14" s="236">
-        <f>J13*(1-Model!L647)</f>
-        <v>926659.971468542</v>
+        <f>IF(Model!J18&gt;0, J13*(1-Model!L647), J13)</f>
+        <v>8446163.0919375382</v>
       </c>
     </row>
     <row r="15" spans="2:10" ht="15" x14ac:dyDescent="0.35">
       <c r="B15" s="397" t="s">
+        <v>440</v>
+      </c>
+      <c r="F15" s="236">
+        <f>Model!H498</f>
+        <v>30000000</v>
+      </c>
+      <c r="G15" s="236">
+        <f>Model!I498</f>
+        <v>30000000</v>
+      </c>
+      <c r="H15" s="236">
+        <f>Model!J498</f>
+        <v>30000000</v>
+      </c>
+      <c r="I15" s="236">
+        <f>Model!K498</f>
+        <v>30000000</v>
+      </c>
+      <c r="J15" s="236">
+        <f>Model!L498</f>
+        <v>30000000</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="B16" s="397" t="s">
         <v>402</v>
       </c>
-      <c r="F15" s="236">
+      <c r="F16" s="236">
         <f>LBO!$F$18</f>
         <v>30000000</v>
       </c>
-      <c r="G15" s="236">
-        <f>LBO!$F$18</f>
-        <v>30000000</v>
-      </c>
-      <c r="H15" s="236">
-        <f>LBO!$F$18</f>
-        <v>30000000</v>
-      </c>
-      <c r="I15" s="236">
-        <f>LBO!$F$18</f>
-        <v>30000000</v>
-      </c>
-      <c r="J15" s="236">
-        <f>LBO!$F$18</f>
-        <v>30000000</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" ht="15" x14ac:dyDescent="0.35">
-      <c r="B16" s="397" t="s">
-        <v>403</v>
-      </c>
-      <c r="F16" s="236">
-        <f>DCF!F17</f>
-        <v>9851507.9020428509</v>
-      </c>
       <c r="G16" s="236">
-        <f>DCF!G17</f>
-        <v>-34368422.195286244</v>
+        <f>F21</f>
+        <v>1784181.0393413212</v>
       </c>
       <c r="H16" s="236">
-        <f>DCF!H17</f>
-        <v>-13309619.642742902</v>
+        <f t="shared" ref="H16:J16" si="2">G21</f>
+        <v>-74747001.508644909</v>
       </c>
       <c r="I16" s="236">
-        <f>DCF!I17</f>
-        <v>11152073.651818261</v>
+        <f t="shared" si="2"/>
+        <v>-131265205.81652763</v>
       </c>
       <c r="J16" s="236">
-        <f>DCF!J17</f>
-        <v>40404904.562844992</v>
+        <f t="shared" si="2"/>
+        <v>-161915784.30578387</v>
       </c>
     </row>
     <row r="17" spans="2:10" ht="15" x14ac:dyDescent="0.35">
       <c r="B17" s="397" t="s">
-        <v>405</v>
+        <v>403</v>
       </c>
       <c r="F17" s="236">
-        <f>F15+F16-F14-F12</f>
-        <v>32280078.488418709</v>
+        <f>DCF!F17</f>
+        <v>-18446232.620498493</v>
       </c>
       <c r="G17" s="236">
-        <f>G15+G16-G14-G12</f>
-        <v>-9362431.2319216952</v>
+        <f>DCF!G17</f>
+        <v>-66859292.07122764</v>
       </c>
       <c r="H17" s="236">
-        <f t="shared" ref="H17:J17" si="2">H15+H16-H14-H12</f>
-        <v>11746311.410987999</v>
+        <f>DCF!H17</f>
+        <v>-46943032.73589173</v>
       </c>
       <c r="I17" s="236">
-        <f t="shared" si="2"/>
-        <v>37167784.529363424</v>
+        <f>DCF!I17</f>
+        <v>-21171158.63298513</v>
       </c>
       <c r="J17" s="236">
-        <f t="shared" si="2"/>
-        <v>69340961.632640377</v>
+        <f>DCF!J17</f>
+        <v>11115300.139815331</v>
       </c>
     </row>
     <row r="18" spans="2:10" ht="15" x14ac:dyDescent="0.35">
       <c r="B18" s="397" t="s">
-        <v>435</v>
+        <v>405</v>
       </c>
       <c r="F18" s="236">
-        <f>MIN(MAX(0,F17), F11-F12)</f>
-        <v>32280078.488418709</v>
+        <f>F16+F17-F14-F12</f>
+        <v>1784181.0393413212</v>
       </c>
       <c r="G18" s="236">
-        <f t="shared" ref="G18:J18" si="3">MIN(MAX(0,G17), G11-G12)</f>
-        <v>0</v>
+        <f>G16+G17-G14-G12</f>
+        <v>-74747001.508644909</v>
       </c>
       <c r="H18" s="236">
-        <f t="shared" si="3"/>
-        <v>11746311.410987999</v>
+        <f t="shared" ref="H18:J18" si="3">H16+H17-H14-H12</f>
+        <v>-131265205.81652763</v>
       </c>
       <c r="I18" s="236">
         <f t="shared" si="3"/>
-        <v>37167784.529363424</v>
+        <v>-161915784.30578387</v>
       </c>
       <c r="J18" s="236">
         <f t="shared" si="3"/>
-        <v>13591012.91487195</v>
+        <v>-160185109.82367691</v>
       </c>
     </row>
     <row r="19" spans="2:10" ht="15" x14ac:dyDescent="0.35">
-      <c r="B19" s="230" t="s">
-        <v>406</v>
-      </c>
-      <c r="C19" s="231"/>
-      <c r="D19" s="231"/>
-      <c r="E19" s="232"/>
-      <c r="F19" s="355">
-        <f>F11-F12-F18</f>
-        <v>64438826.279167116</v>
-      </c>
-      <c r="G19" s="355">
-        <f t="shared" ref="G19:J19" si="4">G11-G12-G18</f>
-        <v>63794438.016375445</v>
-      </c>
-      <c r="H19" s="355">
+      <c r="B19" s="397" t="s">
+        <v>435</v>
+      </c>
+      <c r="F19" s="236">
+        <f>MIN(MAX(0,F18-F15), F11-F12)</f>
+        <v>0</v>
+      </c>
+      <c r="G19" s="236">
+        <f t="shared" ref="G19:J19" si="4">MIN(MAX(0,G18-G15), G11-G12)</f>
+        <v>0</v>
+      </c>
+      <c r="H19" s="236">
         <f t="shared" si="4"/>
-        <v>51410182.22522369</v>
-      </c>
-      <c r="I19" s="355">
+        <v>0</v>
+      </c>
+      <c r="I19" s="236">
         <f t="shared" si="4"/>
-        <v>13728295.87360803</v>
-      </c>
-      <c r="J19" s="355">
+        <v>0</v>
+      </c>
+      <c r="J19" s="236">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
     </row>
     <row r="20" spans="2:10" ht="15" x14ac:dyDescent="0.35">
       <c r="B20" s="230" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="C20" s="231"/>
       <c r="D20" s="231"/>
       <c r="E20" s="232"/>
-      <c r="F20" s="263">
-        <f>F17</f>
-        <v>32280078.488418709</v>
-      </c>
-      <c r="G20" s="263">
-        <f t="shared" ref="G20:J20" si="5">G17</f>
-        <v>-9362431.2319216952</v>
-      </c>
-      <c r="H20" s="263">
+      <c r="F20" s="355">
+        <f>F11-F12-F19</f>
+        <v>96718904.767585829</v>
+      </c>
+      <c r="G20" s="355">
+        <f t="shared" ref="G20:J20" si="5">G11-G12-G19</f>
+        <v>95751715.719909966</v>
+      </c>
+      <c r="H20" s="355">
         <f t="shared" si="5"/>
-        <v>11746311.410987999</v>
-      </c>
-      <c r="I20" s="263">
+        <v>94794198.562710866</v>
+      </c>
+      <c r="I20" s="355">
         <f t="shared" si="5"/>
-        <v>37167784.529363424</v>
-      </c>
-      <c r="J20" s="263">
+        <v>93846256.577083752</v>
+      </c>
+      <c r="J20" s="355">
         <f t="shared" si="5"/>
-        <v>69340961.632640377</v>
+        <v>92907794.011312917</v>
       </c>
     </row>
     <row r="21" spans="2:10" ht="15" x14ac:dyDescent="0.35">
       <c r="B21" s="230" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C21" s="231"/>
       <c r="D21" s="231"/>
       <c r="E21" s="232"/>
       <c r="F21" s="263">
-        <f>F19-F20</f>
-        <v>32158747.790748406</v>
+        <f>F18-F19</f>
+        <v>1784181.0393413212</v>
       </c>
       <c r="G21" s="263">
-        <f t="shared" ref="G21:J21" si="6">G19-G20</f>
-        <v>73156869.24829714</v>
+        <f t="shared" ref="G21:J21" si="6">G18-G19</f>
+        <v>-74747001.508644909</v>
       </c>
       <c r="H21" s="263">
         <f t="shared" si="6"/>
-        <v>39663870.814235687</v>
+        <v>-131265205.81652763</v>
       </c>
       <c r="I21" s="263">
         <f t="shared" si="6"/>
-        <v>-23439488.655755393</v>
+        <v>-161915784.30578387</v>
       </c>
       <c r="J21" s="263">
         <f t="shared" si="6"/>
-        <v>-69340961.632640377</v>
+        <v>-160185109.82367691</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10" ht="15" x14ac:dyDescent="0.35">
+      <c r="B22" s="230" t="s">
+        <v>408</v>
+      </c>
+      <c r="C22" s="231"/>
+      <c r="D22" s="231"/>
+      <c r="E22" s="232"/>
+      <c r="F22" s="263">
+        <f>F20-F21</f>
+        <v>94934723.728244513</v>
+      </c>
+      <c r="G22" s="263">
+        <f t="shared" ref="G22:J22" si="7">G20-G21</f>
+        <v>170498717.22855487</v>
+      </c>
+      <c r="H22" s="263">
+        <f t="shared" si="7"/>
+        <v>226059404.37923849</v>
+      </c>
+      <c r="I22" s="263">
+        <f t="shared" si="7"/>
+        <v>255762040.88286763</v>
+      </c>
+      <c r="J22" s="263">
+        <f t="shared" si="7"/>
+        <v>253092903.83498985</v>
       </c>
     </row>
   </sheetData>
